--- a/FNOT.xlsx
+++ b/FNOT.xlsx
@@ -458,7 +458,7 @@
         <v>MONTHLY macd_line</v>
       </c>
       <c r="R1" t="str">
-        <v>MONTLY macd_signal</v>
+        <v>MONTHLY macd_signal</v>
       </c>
       <c r="S1" t="str">
         <v>Add Column</v>
@@ -490,7 +490,7 @@
         <v>17.52</v>
       </c>
       <c r="I2" s="1">
-        <v>45548613</v>
+        <v>45883930</v>
       </c>
       <c r="J2" s="1">
         <v>175.22</v>
@@ -502,7 +502,7 @@
         <v>179.8</v>
       </c>
       <c r="M2" s="3">
-        <v>1.71</v>
+        <v>-1.18</v>
       </c>
       <c r="N2" s="3">
         <v>-2.12</v>
@@ -517,7 +517,7 @@
         <v>15.89</v>
       </c>
       <c r="R2" s="3">
-        <v>-2.12</v>
+        <v>15.9</v>
       </c>
       <c r="S2" t="str">
         <v/>
@@ -549,7 +549,7 @@
         <v>-1.36</v>
       </c>
       <c r="I3" s="1">
-        <v>77910530</v>
+        <v>78115490</v>
       </c>
       <c r="J3" s="1">
         <v>114.2</v>
@@ -561,7 +561,7 @@
         <v>115.95</v>
       </c>
       <c r="M3" s="3">
-        <v>1.63</v>
+        <v>0.74</v>
       </c>
       <c r="N3" s="3">
         <v>0.13</v>
@@ -576,7 +576,7 @@
         <v>4.88</v>
       </c>
       <c r="R3" s="3">
-        <v>0.13</v>
+        <v>5.87</v>
       </c>
       <c r="S3" t="str">
         <v/>
@@ -608,7 +608,7 @@
         <v>-19.5</v>
       </c>
       <c r="I4" s="1">
-        <v>13571340</v>
+        <v>13633759</v>
       </c>
       <c r="J4" s="1">
         <v>266.99</v>
@@ -620,7 +620,7 @@
         <v>238.05</v>
       </c>
       <c r="M4" s="3">
-        <v>-9.44</v>
+        <v>-1.16</v>
       </c>
       <c r="N4" s="3">
         <v>-1.69</v>
@@ -635,7 +635,7 @@
         <v>4.24</v>
       </c>
       <c r="R4" s="3">
-        <v>-1.69</v>
+        <v>11.71</v>
       </c>
       <c r="S4" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>-4.91</v>
       </c>
       <c r="I5" s="1">
-        <v>14517587</v>
+        <v>14616945</v>
       </c>
       <c r="J5" s="1">
         <v>146.63</v>
@@ -679,7 +679,7 @@
         <v>139.02</v>
       </c>
       <c r="M5" s="3">
-        <v>-2.58</v>
+        <v>-1.47</v>
       </c>
       <c r="N5" s="3">
         <v>-1.96</v>
@@ -694,7 +694,7 @@
         <v>7.54</v>
       </c>
       <c r="R5" s="3">
-        <v>-1.96</v>
+        <v>9.7</v>
       </c>
       <c r="S5" t="str">
         <v/>
@@ -726,7 +726,7 @@
         <v>30.61</v>
       </c>
       <c r="I6" s="1">
-        <v>30985612</v>
+        <v>31072948</v>
       </c>
       <c r="J6" s="1">
         <v>307.7</v>
@@ -738,7 +738,7 @@
         <v>340.57</v>
       </c>
       <c r="M6" s="3">
-        <v>11.03</v>
+        <v>-0.25</v>
       </c>
       <c r="N6" s="3">
         <v>-3.44</v>
@@ -753,7 +753,7 @@
         <v>43.53</v>
       </c>
       <c r="R6" s="3">
-        <v>-3.44</v>
+        <v>37.23</v>
       </c>
       <c r="S6" t="str">
         <v/>
@@ -785,7 +785,7 @@
         <v>-21.24</v>
       </c>
       <c r="I7" s="1">
-        <v>30622746</v>
+        <v>31038836</v>
       </c>
       <c r="J7" s="1">
         <v>134.78</v>
@@ -797,7 +797,7 @@
         <v>124.74</v>
       </c>
       <c r="M7" s="3">
-        <v>-3.61</v>
+        <v>-1.27</v>
       </c>
       <c r="N7" s="3">
         <v>-1.61</v>
@@ -812,7 +812,7 @@
         <v>7.21</v>
       </c>
       <c r="R7" s="3">
-        <v>-1.61</v>
+        <v>10.58</v>
       </c>
       <c r="S7" t="str">
         <v/>
@@ -844,7 +844,7 @@
         <v>34.89</v>
       </c>
       <c r="I8" s="1">
-        <v>555753</v>
+        <v>557390</v>
       </c>
       <c r="J8" s="1">
         <v>6645.75</v>
@@ -856,7 +856,7 @@
         <v>7254.82</v>
       </c>
       <c r="M8" s="3">
-        <v>99.9</v>
+        <v>-96.69</v>
       </c>
       <c r="N8" s="3">
         <v>-113.01</v>
@@ -871,7 +871,7 @@
         <v>442.81</v>
       </c>
       <c r="R8" s="3">
-        <v>-113.01</v>
+        <v>359.39</v>
       </c>
       <c r="S8" t="str">
         <v/>
@@ -903,7 +903,7 @@
         <v>6.57</v>
       </c>
       <c r="I9" s="1">
-        <v>3272521</v>
+        <v>3320243</v>
       </c>
       <c r="J9" s="1">
         <v>1241.74</v>
@@ -915,7 +915,7 @@
         <v>1269.77</v>
       </c>
       <c r="M9" s="3">
-        <v>1.38</v>
+        <v>-20.32</v>
       </c>
       <c r="N9" s="3">
         <v>-21.87</v>
@@ -930,7 +930,7 @@
         <v>93.67</v>
       </c>
       <c r="R9" s="3">
-        <v>-21.87</v>
+        <v>97.54</v>
       </c>
       <c r="S9" t="str">
         <v/>
@@ -962,7 +962,7 @@
         <v>30.48</v>
       </c>
       <c r="I10" s="1">
-        <v>14374507</v>
+        <v>14565080</v>
       </c>
       <c r="J10" s="1">
         <v>76.18</v>
@@ -974,7 +974,7 @@
         <v>82.05</v>
       </c>
       <c r="M10" s="3">
-        <v>1.95</v>
+        <v>-0.27</v>
       </c>
       <c r="N10" s="3">
         <v>-0.11</v>
@@ -989,7 +989,7 @@
         <v>8.61</v>
       </c>
       <c r="R10" s="3">
-        <v>-0.11</v>
+        <v>7.54</v>
       </c>
       <c r="S10" t="str">
         <v/>
@@ -1021,7 +1021,7 @@
         <v>-6.4</v>
       </c>
       <c r="I11" s="1">
-        <v>4844993</v>
+        <v>5262091</v>
       </c>
       <c r="J11" s="1">
         <v>255.88</v>
@@ -1033,7 +1033,7 @@
         <v>232.46</v>
       </c>
       <c r="M11" s="3">
-        <v>-9.62</v>
+        <v>-3.13</v>
       </c>
       <c r="N11" s="3">
         <v>-3.37</v>
@@ -1048,7 +1048,7 @@
         <v>0.59</v>
       </c>
       <c r="R11" s="3">
-        <v>-3.37</v>
+        <v>7.02</v>
       </c>
       <c r="S11" t="str">
         <v/>
@@ -1080,7 +1080,7 @@
         <v>-0.87</v>
       </c>
       <c r="I12" s="1">
-        <v>14878713</v>
+        <v>15083265</v>
       </c>
       <c r="J12" s="1">
         <v>1040.36</v>
@@ -1092,7 +1092,7 @@
         <v>1007.47</v>
       </c>
       <c r="M12" s="3">
-        <v>-14.8</v>
+        <v>-12.01</v>
       </c>
       <c r="N12" s="3">
         <v>-15.82</v>
@@ -1107,7 +1107,7 @@
         <v>70.31</v>
       </c>
       <c r="R12" s="3">
-        <v>-15.82</v>
+        <v>81.7</v>
       </c>
       <c r="S12" t="str">
         <v/>
@@ -1139,7 +1139,7 @@
         <v>31.96</v>
       </c>
       <c r="I13" s="1">
-        <v>3920978</v>
+        <v>3963727</v>
       </c>
       <c r="J13" s="1">
         <v>803.91</v>
@@ -1151,7 +1151,7 @@
         <v>881.08</v>
       </c>
       <c r="M13" s="3">
-        <v>15.54</v>
+        <v>-10.51</v>
       </c>
       <c r="N13" s="3">
         <v>-7.29</v>
@@ -1166,7 +1166,7 @@
         <v>83.93</v>
       </c>
       <c r="R13" s="3">
-        <v>-7.29</v>
+        <v>77.65</v>
       </c>
       <c r="S13" t="str">
         <v/>
@@ -1198,7 +1198,7 @@
         <v>29.22</v>
       </c>
       <c r="I14" s="1">
-        <v>6069619</v>
+        <v>6096648</v>
       </c>
       <c r="J14" s="1">
         <v>289.31</v>
@@ -1210,7 +1210,7 @@
         <v>293.5</v>
       </c>
       <c r="M14" s="3">
-        <v>-0.05</v>
+        <v>3.06</v>
       </c>
       <c r="N14" s="3">
         <v>1.14</v>
@@ -1225,7 +1225,7 @@
         <v>16.83</v>
       </c>
       <c r="R14" s="3">
-        <v>1.14</v>
+        <v>15.37</v>
       </c>
       <c r="S14" t="str">
         <v/>
@@ -1257,7 +1257,7 @@
         <v>-10.32</v>
       </c>
       <c r="I15" s="1">
-        <v>2301148</v>
+        <v>2331147</v>
       </c>
       <c r="J15" s="1">
         <v>3947.31</v>
@@ -1269,7 +1269,7 @@
         <v>3898.11</v>
       </c>
       <c r="M15" s="3">
-        <v>-64.97</v>
+        <v>-74.21</v>
       </c>
       <c r="N15" s="3">
         <v>-72.41</v>
@@ -1284,7 +1284,7 @@
         <v>153.91</v>
       </c>
       <c r="R15" s="3">
-        <v>-72.41</v>
+        <v>215.61</v>
       </c>
       <c r="S15" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>5.81</v>
       </c>
       <c r="I16" s="1">
-        <v>910281</v>
+        <v>925310</v>
       </c>
       <c r="J16" s="1">
         <v>462.84</v>
@@ -1328,7 +1328,7 @@
         <v>469.76</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.32</v>
+        <v>-7.71</v>
       </c>
       <c r="N16" s="3">
         <v>-7.51</v>
@@ -1343,7 +1343,7 @@
         <v>23.2</v>
       </c>
       <c r="R16" s="3">
-        <v>-7.51</v>
+        <v>30.22</v>
       </c>
       <c r="S16" t="str">
         <v/>
@@ -1375,7 +1375,7 @@
         <v>0.5</v>
       </c>
       <c r="I17" s="1">
-        <v>482195</v>
+        <v>490129</v>
       </c>
       <c r="J17" s="1">
         <v>7399.85</v>
@@ -1387,7 +1387,7 @@
         <v>7591.19</v>
       </c>
       <c r="M17" s="3">
-        <v>-2.03</v>
+        <v>-98.59</v>
       </c>
       <c r="N17" s="3">
         <v>-151.33</v>
@@ -1402,7 +1402,7 @@
         <v>716.08</v>
       </c>
       <c r="R17" s="3">
-        <v>-151.33</v>
+        <v>762.37</v>
       </c>
       <c r="S17" t="str">
         <v/>
@@ -1434,7 +1434,7 @@
         <v>20.15</v>
       </c>
       <c r="I18" s="1">
-        <v>2407665</v>
+        <v>2526448</v>
       </c>
       <c r="J18" s="1">
         <v>1641.51</v>
@@ -1446,7 +1446,7 @@
         <v>1728.21</v>
       </c>
       <c r="M18" s="3">
-        <v>34.75</v>
+        <v>2.93</v>
       </c>
       <c r="N18" s="3">
         <v>6.13</v>
@@ -1461,7 +1461,7 @@
         <v>149.44</v>
       </c>
       <c r="R18" s="3">
-        <v>6.13</v>
+        <v>135.3</v>
       </c>
       <c r="S18" t="str">
         <v/>
@@ -1493,7 +1493,7 @@
         <v>-2.27</v>
       </c>
       <c r="I19" s="1">
-        <v>993043</v>
+        <v>1023837</v>
       </c>
       <c r="J19" s="1">
         <v>1243.77</v>
@@ -1505,7 +1505,7 @@
         <v>1188.9</v>
       </c>
       <c r="M19" s="3">
-        <v>-13.1</v>
+        <v>12.25</v>
       </c>
       <c r="N19" s="3">
         <v>10.06</v>
@@ -1520,7 +1520,7 @@
         <v>13.8</v>
       </c>
       <c r="R19" s="3">
-        <v>10.06</v>
+        <v>25.96</v>
       </c>
       <c r="S19" t="str">
         <v/>
@@ -1552,7 +1552,7 @@
         <v>-30.17</v>
       </c>
       <c r="I20" s="1">
-        <v>3939743</v>
+        <v>3972010</v>
       </c>
       <c r="J20" s="1">
         <v>390.83</v>
@@ -1564,7 +1564,7 @@
         <v>357.56</v>
       </c>
       <c r="M20" s="3">
-        <v>-14.47</v>
+        <v>-4.91</v>
       </c>
       <c r="N20" s="3">
         <v>-6.62</v>
@@ -1579,7 +1579,7 @@
         <v>7.46</v>
       </c>
       <c r="R20" s="3">
-        <v>-6.62</v>
+        <v>22.34</v>
       </c>
       <c r="S20" t="str">
         <v/>
@@ -1611,7 +1611,7 @@
         <v>42.98</v>
       </c>
       <c r="I21" s="1">
-        <v>1147922</v>
+        <v>1155788</v>
       </c>
       <c r="J21" s="1">
         <v>2807.95</v>
@@ -1623,7 +1623,7 @@
         <v>3207.69</v>
       </c>
       <c r="M21" s="3">
-        <v>166.94</v>
+        <v>2.66</v>
       </c>
       <c r="N21" s="3">
         <v>23.8</v>
@@ -1638,7 +1638,7 @@
         <v>576.88</v>
       </c>
       <c r="R21" s="3">
-        <v>23.8</v>
+        <v>505.78</v>
       </c>
       <c r="S21" t="str">
         <v/>
@@ -1670,7 +1670,7 @@
         <v>7.96</v>
       </c>
       <c r="I22" s="1">
-        <v>172610</v>
+        <v>174317</v>
       </c>
       <c r="J22" s="1">
         <v>3581.84</v>
@@ -1682,7 +1682,7 @@
         <v>3514.52</v>
       </c>
       <c r="M22" s="3">
-        <v>-18.82</v>
+        <v>28.52</v>
       </c>
       <c r="N22" s="3">
         <v>9.3</v>
@@ -1697,7 +1697,7 @@
         <v>-131.15</v>
       </c>
       <c r="R22" s="3">
-        <v>9.3</v>
+        <v>-91.26</v>
       </c>
       <c r="S22" t="str">
         <v/>
@@ -1729,7 +1729,7 @@
         <v>-13.67</v>
       </c>
       <c r="I23" s="1">
-        <v>6536590</v>
+        <v>6633009</v>
       </c>
       <c r="J23" s="1">
         <v>99.23</v>
@@ -1756,7 +1756,7 @@
         <v>5.63</v>
       </c>
       <c r="R23" s="3">
-        <v>-2.09</v>
+        <v>7.24</v>
       </c>
       <c r="S23" t="str">
         <v/>
@@ -1788,7 +1788,7 @@
         <v>-0.56</v>
       </c>
       <c r="I24" s="1">
-        <v>24154</v>
+        <v>25967</v>
       </c>
       <c r="J24" s="1">
         <v>10666.37</v>
@@ -1800,7 +1800,7 @@
         <v>11126.5</v>
       </c>
       <c r="M24" s="3">
-        <v>98.07</v>
+        <v>-2.36</v>
       </c>
       <c r="N24" s="3">
         <v>-72.08</v>
@@ -1815,7 +1815,7 @@
         <v>292.01</v>
       </c>
       <c r="R24" s="3">
-        <v>-72.08</v>
+        <v>481.61</v>
       </c>
       <c r="S24" t="str">
         <v/>
@@ -1847,7 +1847,7 @@
         <v>-34.15</v>
       </c>
       <c r="I25" s="1">
-        <v>1499727</v>
+        <v>1501957</v>
       </c>
       <c r="J25" s="1">
         <v>673.67</v>
@@ -1859,7 +1859,7 @@
         <v>621.27</v>
       </c>
       <c r="M25" s="3">
-        <v>-30.33</v>
+        <v>-17.95</v>
       </c>
       <c r="N25" s="3">
         <v>-19.29</v>
@@ -1874,7 +1874,7 @@
         <v>-54.89</v>
       </c>
       <c r="R25" s="3">
-        <v>-19.29</v>
+        <v>-31.44</v>
       </c>
       <c r="S25" t="str">
         <v/>
@@ -1906,7 +1906,7 @@
         <v>-34.96</v>
       </c>
       <c r="I26" s="1">
-        <v>1552809</v>
+        <v>1571724</v>
       </c>
       <c r="J26" s="1">
         <v>446.16</v>
@@ -1918,7 +1918,7 @@
         <v>390.3</v>
       </c>
       <c r="M26" s="3">
-        <v>-26.56</v>
+        <v>-11.07</v>
       </c>
       <c r="N26" s="3">
         <v>-12.42</v>
@@ -1933,7 +1933,7 @@
         <v>-38.18</v>
       </c>
       <c r="R26" s="3">
-        <v>-12.42</v>
+        <v>-19.47</v>
       </c>
       <c r="S26" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>86.73</v>
       </c>
       <c r="I27" s="1">
-        <v>1085894</v>
+        <v>1133053</v>
       </c>
       <c r="J27" s="1">
         <v>1408.13</v>
@@ -1977,7 +1977,7 @@
         <v>1934.9</v>
       </c>
       <c r="M27" s="3">
-        <v>211.87</v>
+        <v>37.14</v>
       </c>
       <c r="N27" s="3">
         <v>39.27</v>
@@ -1992,7 +1992,7 @@
         <v>353.69</v>
       </c>
       <c r="R27" s="3">
-        <v>39.27</v>
+        <v>250.08</v>
       </c>
       <c r="S27" t="str">
         <v/>
@@ -2024,7 +2024,7 @@
         <v>2.34</v>
       </c>
       <c r="I28" s="1">
-        <v>1086882</v>
+        <v>1105179</v>
       </c>
       <c r="J28" s="1">
         <v>864.41</v>
@@ -2036,7 +2036,7 @@
         <v>854.46</v>
       </c>
       <c r="M28" s="3">
-        <v>-2.36</v>
+        <v>-0.53</v>
       </c>
       <c r="N28" s="3">
         <v>-6.83</v>
@@ -2051,7 +2051,7 @@
         <v>87.49</v>
       </c>
       <c r="R28" s="3">
-        <v>-6.83</v>
+        <v>99.38</v>
       </c>
       <c r="S28" t="str">
         <v/>
@@ -2083,7 +2083,7 @@
         <v>-7.11</v>
       </c>
       <c r="I29" s="1">
-        <v>552081</v>
+        <v>576282</v>
       </c>
       <c r="J29" s="1">
         <v>4812.28</v>
@@ -2095,7 +2095,7 @@
         <v>5017.75</v>
       </c>
       <c r="M29" s="3">
-        <v>-19.97</v>
+        <v>-77.29</v>
       </c>
       <c r="N29" s="3">
         <v>-61.29</v>
@@ -2110,7 +2110,7 @@
         <v>209.88</v>
       </c>
       <c r="R29" s="3">
-        <v>-61.29</v>
+        <v>317.01</v>
       </c>
       <c r="S29" t="str">
         <v/>
@@ -2142,7 +2142,7 @@
         <v>-23.36</v>
       </c>
       <c r="I30" s="1">
-        <v>2288307</v>
+        <v>2432283</v>
       </c>
       <c r="J30" s="1">
         <v>320.6</v>
@@ -2154,7 +2154,7 @@
         <v>307.39</v>
       </c>
       <c r="M30" s="3">
-        <v>-5.81</v>
+        <v>-5.01</v>
       </c>
       <c r="N30" s="3">
         <v>-5.14</v>
@@ -2169,7 +2169,7 @@
         <v>6.56</v>
       </c>
       <c r="R30" s="3">
-        <v>-5.14</v>
+        <v>14.56</v>
       </c>
       <c r="S30" t="str">
         <v/>
@@ -2201,7 +2201,7 @@
         <v>-9.22</v>
       </c>
       <c r="I31" s="1">
-        <v>190669</v>
+        <v>194246</v>
       </c>
       <c r="J31" s="1">
         <v>1686.88</v>
@@ -2213,7 +2213,7 @@
         <v>1519.3</v>
       </c>
       <c r="M31" s="3">
-        <v>-43.76</v>
+        <v>15.43</v>
       </c>
       <c r="N31" s="3">
         <v>10.93</v>
@@ -2228,7 +2228,7 @@
         <v>21.93</v>
       </c>
       <c r="R31" s="3">
-        <v>10.93</v>
+        <v>82.97</v>
       </c>
       <c r="S31" t="str">
         <v/>
@@ -2260,7 +2260,7 @@
         <v>3.36</v>
       </c>
       <c r="I32" s="1">
-        <v>1309935</v>
+        <v>1333698</v>
       </c>
       <c r="J32" s="1">
         <v>282.34</v>
@@ -2272,7 +2272,7 @@
         <v>288.23</v>
       </c>
       <c r="M32" s="3">
-        <v>3.6</v>
+        <v>1.77</v>
       </c>
       <c r="N32" s="3">
         <v>1.4</v>
@@ -2287,7 +2287,7 @@
         <v>0.76</v>
       </c>
       <c r="R32" s="3">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="str">
         <v/>
@@ -2319,7 +2319,7 @@
         <v>39.05</v>
       </c>
       <c r="I33" s="1">
-        <v>234541</v>
+        <v>235630</v>
       </c>
       <c r="J33" s="1">
         <v>1836.42</v>
@@ -2331,7 +2331,7 @@
         <v>2167.26</v>
       </c>
       <c r="M33" s="3">
-        <v>106.17</v>
+        <v>-8.28</v>
       </c>
       <c r="N33" s="3">
         <v>-13.1</v>
@@ -2346,7 +2346,7 @@
         <v>331.99</v>
       </c>
       <c r="R33" s="3">
-        <v>-13.1</v>
+        <v>285.73</v>
       </c>
       <c r="S33" t="str">
         <v/>
@@ -2378,7 +2378,7 @@
         <v>-16.54</v>
       </c>
       <c r="I34" s="1">
-        <v>1062442</v>
+        <v>1076545</v>
       </c>
       <c r="J34" s="1">
         <v>902.67</v>
@@ -2390,7 +2390,7 @@
         <v>865.64</v>
       </c>
       <c r="M34" s="3">
-        <v>-40.25</v>
+        <v>-39.02</v>
       </c>
       <c r="N34" s="3">
         <v>-36.79</v>
@@ -2405,7 +2405,7 @@
         <v>68.4</v>
       </c>
       <c r="R34" s="3">
-        <v>-36.79</v>
+        <v>100.86</v>
       </c>
       <c r="S34" t="str">
         <v/>
@@ -2437,7 +2437,7 @@
         <v>-9.37</v>
       </c>
       <c r="I35" s="1">
-        <v>347330</v>
+        <v>366042</v>
       </c>
       <c r="J35" s="1">
         <v>5302.9</v>
@@ -2449,7 +2449,7 @@
         <v>5387.04</v>
       </c>
       <c r="M35" s="3">
-        <v>-6.07</v>
+        <v>-60.06</v>
       </c>
       <c r="N35" s="3">
         <v>-85.68</v>
@@ -2464,7 +2464,7 @@
         <v>253.62</v>
       </c>
       <c r="R35" s="3">
-        <v>-85.68</v>
+        <v>308</v>
       </c>
       <c r="S35" t="str">
         <v/>
@@ -2496,7 +2496,7 @@
         <v>4.01</v>
       </c>
       <c r="I36" s="1">
-        <v>211828</v>
+        <v>218940</v>
       </c>
       <c r="J36" s="1">
         <v>5014.61</v>
@@ -2508,7 +2508,7 @@
         <v>5044.59</v>
       </c>
       <c r="M36" s="3">
-        <v>-90.59</v>
+        <v>-110.06</v>
       </c>
       <c r="N36" s="3">
         <v>-96.43</v>
@@ -2523,7 +2523,7 @@
         <v>573</v>
       </c>
       <c r="R36" s="3">
-        <v>-96.43</v>
+        <v>616.77</v>
       </c>
       <c r="S36" t="str">
         <v/>
@@ -2555,7 +2555,7 @@
         <v>-5.61</v>
       </c>
       <c r="I37" s="1">
-        <v>5164102</v>
+        <v>5419051</v>
       </c>
       <c r="J37" s="1">
         <v>417.08</v>
@@ -2567,7 +2567,7 @@
         <v>397.19</v>
       </c>
       <c r="M37" s="3">
-        <v>-10.38</v>
+        <v>-5.9</v>
       </c>
       <c r="N37" s="3">
         <v>-6.22</v>
@@ -2582,7 +2582,7 @@
         <v>34.67</v>
       </c>
       <c r="R37" s="3">
-        <v>-6.22</v>
+        <v>46.73</v>
       </c>
       <c r="S37" t="str">
         <v/>
@@ -2614,7 +2614,7 @@
         <v>2.84</v>
       </c>
       <c r="I38" s="1">
-        <v>239383</v>
+        <v>243811</v>
       </c>
       <c r="J38" s="1">
         <v>1502.88</v>
@@ -2626,7 +2626,7 @@
         <v>1454.65</v>
       </c>
       <c r="M38" s="3">
-        <v>-26.86</v>
+        <v>-1.4</v>
       </c>
       <c r="N38" s="3">
         <v>-9.35</v>
@@ -2641,7 +2641,7 @@
         <v>-54.46</v>
       </c>
       <c r="R38" s="3">
-        <v>-9.35</v>
+        <v>-55.66</v>
       </c>
       <c r="S38" t="str">
         <v/>
@@ -2673,7 +2673,7 @@
         <v>18.41</v>
       </c>
       <c r="I39" s="1">
-        <v>243467</v>
+        <v>250305</v>
       </c>
       <c r="J39" s="1">
         <v>4483.14</v>
@@ -2685,7 +2685,7 @@
         <v>4861.57</v>
       </c>
       <c r="M39" s="3">
-        <v>91.7</v>
+        <v>-90.75</v>
       </c>
       <c r="N39" s="3">
         <v>-70.25</v>
@@ -2700,7 +2700,7 @@
         <v>519.23</v>
       </c>
       <c r="R39" s="3">
-        <v>-70.25</v>
+        <v>487.07</v>
       </c>
       <c r="S39" t="str">
         <v/>
@@ -2732,7 +2732,7 @@
         <v>-10.43</v>
       </c>
       <c r="I40" s="1">
-        <v>759919</v>
+        <v>765440</v>
       </c>
       <c r="J40" s="1">
         <v>2382.66</v>
@@ -2744,7 +2744,7 @@
         <v>2381.69</v>
       </c>
       <c r="M40" s="3">
-        <v>5.02</v>
+        <v>36.12</v>
       </c>
       <c r="N40" s="3">
         <v>5.25</v>
@@ -2759,7 +2759,7 @@
         <v>-66.67</v>
       </c>
       <c r="R40" s="3">
-        <v>5.25</v>
+        <v>-38.21</v>
       </c>
       <c r="S40" t="str">
         <v/>
@@ -2791,7 +2791,7 @@
         <v>-14.99</v>
       </c>
       <c r="I41" s="1">
-        <v>3866884</v>
+        <v>3994293</v>
       </c>
       <c r="J41" s="1">
         <v>1333.87</v>
@@ -2803,7 +2803,7 @@
         <v>1286.81</v>
       </c>
       <c r="M41" s="3">
-        <v>-2.49</v>
+        <v>21.5</v>
       </c>
       <c r="N41" s="3">
         <v>0.25</v>
@@ -2818,7 +2818,7 @@
         <v>-57.09</v>
       </c>
       <c r="R41" s="3">
-        <v>0.25</v>
+        <v>-30.74</v>
       </c>
       <c r="S41" t="str">
         <v/>
@@ -2850,7 +2850,7 @@
         <v>18.27</v>
       </c>
       <c r="I42" s="1">
-        <v>110595</v>
+        <v>113112</v>
       </c>
       <c r="J42" s="1">
         <v>3534.89</v>
@@ -2862,7 +2862,7 @@
         <v>3877.78</v>
       </c>
       <c r="M42" s="3">
-        <v>55.36</v>
+        <v>-61.37</v>
       </c>
       <c r="N42" s="3">
         <v>-53.38</v>
@@ -2877,7 +2877,7 @@
         <v>197.03</v>
       </c>
       <c r="R42" s="3">
-        <v>-53.38</v>
+        <v>179</v>
       </c>
       <c r="S42" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>-5.39</v>
       </c>
       <c r="I43" s="1">
-        <v>8656077</v>
+        <v>8908653</v>
       </c>
       <c r="J43" s="1">
         <v>283.11</v>
@@ -2921,7 +2921,7 @@
         <v>262.94</v>
       </c>
       <c r="M43" s="3">
-        <v>-9.74</v>
+        <v>-4.76</v>
       </c>
       <c r="N43" s="3">
         <v>-4.54</v>
@@ -2936,7 +2936,7 @@
         <v>0.03</v>
       </c>
       <c r="R43" s="3">
-        <v>-4.54</v>
+        <v>6.48</v>
       </c>
       <c r="S43" t="str">
         <v/>
@@ -2968,7 +2968,7 @@
         <v>-15.84</v>
       </c>
       <c r="I44" s="1">
-        <v>463141</v>
+        <v>497488</v>
       </c>
       <c r="J44" s="1">
         <v>2539.18</v>
@@ -2980,7 +2980,7 @@
         <v>2509.31</v>
       </c>
       <c r="M44" s="3">
-        <v>-57.89</v>
+        <v>-47.82</v>
       </c>
       <c r="N44" s="3">
         <v>-50.74</v>
@@ -2995,7 +2995,7 @@
         <v>-58.18</v>
       </c>
       <c r="R44" s="3">
-        <v>-50.74</v>
+        <v>-68.44</v>
       </c>
       <c r="S44" t="str">
         <v/>
@@ -3027,7 +3027,7 @@
         <v>32.86</v>
       </c>
       <c r="I45" s="1">
-        <v>1286461</v>
+        <v>1303809</v>
       </c>
       <c r="J45" s="1">
         <v>1300.9</v>
@@ -3039,7 +3039,7 @@
         <v>1431.11</v>
       </c>
       <c r="M45" s="3">
-        <v>11.82</v>
+        <v>-22.37</v>
       </c>
       <c r="N45" s="3">
         <v>-36.46</v>
@@ -3054,7 +3054,7 @@
         <v>104.91</v>
       </c>
       <c r="R45" s="3">
-        <v>-36.46</v>
+        <v>50.53</v>
       </c>
       <c r="S45" t="str">
         <v/>
@@ -3086,7 +3086,7 @@
         <v>-12.39</v>
       </c>
       <c r="I46" s="1">
-        <v>1358285</v>
+        <v>1387215</v>
       </c>
       <c r="J46" s="1">
         <v>1370.69</v>
@@ -3098,7 +3098,7 @@
         <v>1387.23</v>
       </c>
       <c r="M46" s="3">
-        <v>-15.29</v>
+        <v>-19.77</v>
       </c>
       <c r="N46" s="3">
         <v>-20.37</v>
@@ -3113,7 +3113,7 @@
         <v>-4.15</v>
       </c>
       <c r="R46" s="3">
-        <v>-20.37</v>
+        <v>15.85</v>
       </c>
       <c r="S46" t="str">
         <v/>
@@ -3145,7 +3145,7 @@
         <v>-0.05</v>
       </c>
       <c r="I47" s="1">
-        <v>1392170</v>
+        <v>1408997</v>
       </c>
       <c r="J47" s="1">
         <v>523.25</v>
@@ -3157,7 +3157,7 @@
         <v>519.93</v>
       </c>
       <c r="M47" s="3">
-        <v>-13.19</v>
+        <v>-12.59</v>
       </c>
       <c r="N47" s="3">
         <v>-13.94</v>
@@ -3172,7 +3172,7 @@
         <v>5.76</v>
       </c>
       <c r="R47" s="3">
-        <v>-13.94</v>
+        <v>12.53</v>
       </c>
       <c r="S47" t="str">
         <v/>
@@ -3204,7 +3204,7 @@
         <v>19.27</v>
       </c>
       <c r="I48" s="1">
-        <v>20955712</v>
+        <v>20990086</v>
       </c>
       <c r="J48" s="1">
         <v>60.96</v>
@@ -3216,7 +3216,7 @@
         <v>66.59</v>
       </c>
       <c r="M48" s="3">
-        <v>1.46</v>
+        <v>-0.64</v>
       </c>
       <c r="N48" s="3">
         <v>-0.65</v>
@@ -3231,7 +3231,7 @@
         <v>6.35</v>
       </c>
       <c r="R48" s="3">
-        <v>-0.65</v>
+        <v>5.21</v>
       </c>
       <c r="S48" t="str">
         <v/>
@@ -3263,7 +3263,7 @@
         <v>-21.75</v>
       </c>
       <c r="I49" s="1">
-        <v>4397585</v>
+        <v>4567989</v>
       </c>
       <c r="J49" s="1">
         <v>146.77</v>
@@ -3275,7 +3275,7 @@
         <v>135.06</v>
       </c>
       <c r="M49" s="3">
-        <v>-4.45</v>
+        <v>-2.05</v>
       </c>
       <c r="N49" s="3">
         <v>-2.22</v>
@@ -3290,7 +3290,7 @@
         <v>0.56</v>
       </c>
       <c r="R49" s="3">
-        <v>-2.22</v>
+        <v>4.6</v>
       </c>
       <c r="S49" t="str">
         <v/>
@@ -3322,7 +3322,7 @@
         <v>-31.28</v>
       </c>
       <c r="I50" s="1">
-        <v>443674</v>
+        <v>453832</v>
       </c>
       <c r="J50" s="1">
         <v>13689.93</v>
@@ -3334,7 +3334,7 @@
         <v>12597.98</v>
       </c>
       <c r="M50" s="3">
-        <v>-639.4</v>
+        <v>-345.42</v>
       </c>
       <c r="N50" s="3">
         <v>-391.76</v>
@@ -3349,7 +3349,7 @@
         <v>224.9</v>
       </c>
       <c r="R50" s="3">
-        <v>-391.76</v>
+        <v>663.9</v>
       </c>
       <c r="S50" t="str">
         <v/>
@@ -3381,7 +3381,7 @@
         <v>-23.25</v>
       </c>
       <c r="I51" s="1">
-        <v>8603407</v>
+        <v>8676373</v>
       </c>
       <c r="J51" s="1">
         <v>2461.31</v>
@@ -3393,7 +3393,7 @@
         <v>2243.38</v>
       </c>
       <c r="M51" s="3">
-        <v>-55.19</v>
+        <v>46.26</v>
       </c>
       <c r="N51" s="3">
         <v>-3.23</v>
@@ -3408,7 +3408,7 @@
         <v>-354.92</v>
       </c>
       <c r="R51" s="3">
-        <v>-3.23</v>
+        <v>-305.99</v>
       </c>
       <c r="S51" t="str">
         <v/>
@@ -3440,7 +3440,7 @@
         <v>6.75</v>
       </c>
       <c r="I52" s="1">
-        <v>1555074</v>
+        <v>1561240</v>
       </c>
       <c r="J52" s="1">
         <v>931.94</v>
@@ -3452,7 +3452,7 @@
         <v>960.3</v>
       </c>
       <c r="M52" s="3">
-        <v>-21.06</v>
+        <v>-13.8</v>
       </c>
       <c r="N52" s="3">
         <v>-19.38</v>
@@ -3467,7 +3467,7 @@
         <v>-27.29</v>
       </c>
       <c r="R52" s="3">
-        <v>-19.38</v>
+        <v>-29.13</v>
       </c>
       <c r="S52" t="str">
         <v/>
@@ -3499,7 +3499,7 @@
         <v>-8.68</v>
       </c>
       <c r="I53" s="1">
-        <v>4633681</v>
+        <v>4693865</v>
       </c>
       <c r="J53" s="1">
         <v>411.78</v>
@@ -3511,7 +3511,7 @@
         <v>377.9</v>
       </c>
       <c r="M53" s="3">
-        <v>-8.92</v>
+        <v>0.67</v>
       </c>
       <c r="N53" s="3">
         <v>-0.06</v>
@@ -3526,7 +3526,7 @@
         <v>18.9</v>
       </c>
       <c r="R53" s="3">
-        <v>-0.06</v>
+        <v>27.74</v>
       </c>
       <c r="S53" t="str">
         <v/>
@@ -3558,7 +3558,7 @@
         <v>-6.47</v>
       </c>
       <c r="I54" s="1">
-        <v>7819970</v>
+        <v>7892261</v>
       </c>
       <c r="J54" s="1">
         <v>399.12</v>
@@ -3570,7 +3570,7 @@
         <v>350.2</v>
       </c>
       <c r="M54" s="3">
-        <v>-23.27</v>
+        <v>-4.38</v>
       </c>
       <c r="N54" s="3">
         <v>-6.81</v>
@@ -3585,7 +3585,7 @@
         <v>-1.22</v>
       </c>
       <c r="R54" s="3">
-        <v>-6.81</v>
+        <v>12.52</v>
       </c>
       <c r="S54" t="str">
         <v/>
@@ -3617,7 +3617,7 @@
         <v>-12.09</v>
       </c>
       <c r="I55" s="1">
-        <v>3030328</v>
+        <v>3040983</v>
       </c>
       <c r="J55" s="1">
         <v>584.65</v>
@@ -3629,7 +3629,7 @@
         <v>576.89</v>
       </c>
       <c r="M55" s="3">
-        <v>-3.12</v>
+        <v>-11.79</v>
       </c>
       <c r="N55" s="3">
         <v>-9.85</v>
@@ -3644,7 +3644,7 @@
         <v>35.66</v>
       </c>
       <c r="R55" s="3">
-        <v>-9.85</v>
+        <v>39.57</v>
       </c>
       <c r="S55" t="str">
         <v/>
@@ -3676,7 +3676,7 @@
         <v>-2.12</v>
       </c>
       <c r="I56" s="1">
-        <v>2483929</v>
+        <v>2504625</v>
       </c>
       <c r="J56" s="1">
         <v>626.72</v>
@@ -3688,7 +3688,7 @@
         <v>664.53</v>
       </c>
       <c r="M56" s="3">
-        <v>10.29</v>
+        <v>1.72</v>
       </c>
       <c r="N56" s="3">
         <v>-0.14</v>
@@ -3703,7 +3703,7 @@
         <v>-10.59</v>
       </c>
       <c r="R56" s="3">
-        <v>-0.14</v>
+        <v>-7.29</v>
       </c>
       <c r="S56" t="str">
         <v/>
@@ -3735,7 +3735,7 @@
         <v>-1.14</v>
       </c>
       <c r="I57" s="1">
-        <v>924811</v>
+        <v>935822</v>
       </c>
       <c r="J57" s="1">
         <v>1138.34</v>
@@ -3747,7 +3747,7 @@
         <v>1114.51</v>
       </c>
       <c r="M57" s="3">
-        <v>-17.11</v>
+        <v>-27.11</v>
       </c>
       <c r="N57" s="3">
         <v>-22.88</v>
@@ -3762,7 +3762,7 @@
         <v>75.28</v>
       </c>
       <c r="R57" s="3">
-        <v>-22.88</v>
+        <v>90.54</v>
       </c>
       <c r="S57" t="str">
         <v/>
@@ -3794,7 +3794,7 @@
         <v>-19.92</v>
       </c>
       <c r="I58" s="1">
-        <v>4834940</v>
+        <v>5032735</v>
       </c>
       <c r="J58" s="1">
         <v>290.91</v>
@@ -3806,7 +3806,7 @@
         <v>296.48</v>
       </c>
       <c r="M58" s="3">
-        <v>-5.6</v>
+        <v>-12.27</v>
       </c>
       <c r="N58" s="3">
         <v>-12</v>
@@ -3821,7 +3821,7 @@
         <v>32.05</v>
       </c>
       <c r="R58" s="3">
-        <v>-12</v>
+        <v>36.13</v>
       </c>
       <c r="S58" t="str">
         <v/>
@@ -3853,7 +3853,7 @@
         <v>12.05</v>
       </c>
       <c r="I59" s="1">
-        <v>374217</v>
+        <v>381848</v>
       </c>
       <c r="J59" s="1">
         <v>2003.65</v>
@@ -3865,7 +3865,7 @@
         <v>2148.68</v>
       </c>
       <c r="M59" s="3">
-        <v>69.8</v>
+        <v>0.02</v>
       </c>
       <c r="N59" s="3">
         <v>2.5</v>
@@ -3880,7 +3880,7 @@
         <v>157.56</v>
       </c>
       <c r="R59" s="3">
-        <v>2.5</v>
+        <v>141.5</v>
       </c>
       <c r="S59" t="str">
         <v/>
@@ -3912,7 +3912,7 @@
         <v>29.79</v>
       </c>
       <c r="I60" s="1">
-        <v>1344973</v>
+        <v>1374419</v>
       </c>
       <c r="J60" s="1">
         <v>1295.74</v>
@@ -3924,7 +3924,7 @@
         <v>1678.08</v>
       </c>
       <c r="M60" s="3">
-        <v>140.29</v>
+        <v>5.4</v>
       </c>
       <c r="N60" s="3">
         <v>10.03</v>
@@ -3939,7 +3939,7 @@
         <v>189.01</v>
       </c>
       <c r="R60" s="3">
-        <v>10.03</v>
+        <v>132.62</v>
       </c>
       <c r="S60" t="str">
         <v/>
@@ -3971,7 +3971,7 @@
         <v>-7.21</v>
       </c>
       <c r="I61" s="1">
-        <v>3176883</v>
+        <v>3247837</v>
       </c>
       <c r="J61" s="1">
         <v>384.22</v>
@@ -3983,7 +3983,7 @@
         <v>363.46</v>
       </c>
       <c r="M61" s="3">
-        <v>-11.02</v>
+        <v>-4.41</v>
       </c>
       <c r="N61" s="3">
         <v>-5.16</v>
@@ -3998,7 +3998,7 @@
         <v>3.22</v>
       </c>
       <c r="R61" s="3">
-        <v>-5.16</v>
+        <v>12.14</v>
       </c>
       <c r="S61" t="str">
         <v/>
@@ -4030,7 +4030,7 @@
         <v>9.2</v>
       </c>
       <c r="I62" s="1">
-        <v>628106</v>
+        <v>651506</v>
       </c>
       <c r="J62" s="1">
         <v>4432.61</v>
@@ -4042,7 +4042,7 @@
         <v>4859.08</v>
       </c>
       <c r="M62" s="3">
-        <v>68.61</v>
+        <v>-127.95</v>
       </c>
       <c r="N62" s="3">
         <v>-125.75</v>
@@ -4057,7 +4057,7 @@
         <v>364.92</v>
       </c>
       <c r="R62" s="3">
-        <v>-125.75</v>
+        <v>318.16</v>
       </c>
       <c r="S62" t="str">
         <v/>
@@ -4089,7 +4089,7 @@
         <v>-21.63</v>
       </c>
       <c r="I63" s="1">
-        <v>2056600</v>
+        <v>2142503</v>
       </c>
       <c r="J63" s="1">
         <v>3236.65</v>
@@ -4101,7 +4101,7 @@
         <v>3136.56</v>
       </c>
       <c r="M63" s="3">
-        <v>-90.55</v>
+        <v>-72.95</v>
       </c>
       <c r="N63" s="3">
         <v>-90.34</v>
@@ -4116,7 +4116,7 @@
         <v>157.26</v>
       </c>
       <c r="R63" s="3">
-        <v>-90.34</v>
+        <v>257.23</v>
       </c>
       <c r="S63" t="str">
         <v/>
@@ -4148,7 +4148,7 @@
         <v>-2.82</v>
       </c>
       <c r="I64" s="1">
-        <v>2973130</v>
+        <v>3179082</v>
       </c>
       <c r="J64" s="1">
         <v>166.13</v>
@@ -4160,7 +4160,7 @@
         <v>172.25</v>
       </c>
       <c r="M64" s="3">
-        <v>0.61</v>
+        <v>-1.43</v>
       </c>
       <c r="N64" s="3">
         <v>-1.3</v>
@@ -4175,7 +4175,7 @@
         <v>0.16</v>
       </c>
       <c r="R64" s="3">
-        <v>-1.3</v>
+        <v>1.56</v>
       </c>
       <c r="S64" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>9.52</v>
       </c>
       <c r="I65" s="1">
-        <v>462139</v>
+        <v>472084</v>
       </c>
       <c r="J65" s="1">
         <v>3779.36</v>
@@ -4219,7 +4219,7 @@
         <v>4180.38</v>
       </c>
       <c r="M65" s="3">
-        <v>122.92</v>
+        <v>-34.31</v>
       </c>
       <c r="N65" s="3">
         <v>-49.41</v>
@@ -4234,7 +4234,7 @@
         <v>473.35</v>
       </c>
       <c r="R65" s="3">
-        <v>-49.41</v>
+        <v>454.91</v>
       </c>
       <c r="S65" t="str">
         <v/>
@@ -4266,7 +4266,7 @@
         <v>27.59</v>
       </c>
       <c r="I66" s="1">
-        <v>956273</v>
+        <v>965167</v>
       </c>
       <c r="J66" s="1">
         <v>1211.1</v>
@@ -4278,7 +4278,7 @@
         <v>1299.11</v>
       </c>
       <c r="M66" s="3">
-        <v>14.13</v>
+        <v>-1.53</v>
       </c>
       <c r="N66" s="3">
         <v>-5.88</v>
@@ -4293,7 +4293,7 @@
         <v>9.81</v>
       </c>
       <c r="R66" s="3">
-        <v>-5.88</v>
+        <v>-34.27</v>
       </c>
       <c r="S66" t="str">
         <v/>
@@ -4325,7 +4325,7 @@
         <v>-19.02</v>
       </c>
       <c r="I67" s="1">
-        <v>927016</v>
+        <v>948959</v>
       </c>
       <c r="J67" s="1">
         <v>1864.79</v>
@@ -4337,7 +4337,7 @@
         <v>1739.06</v>
       </c>
       <c r="M67" s="3">
-        <v>-51.11</v>
+        <v>-24.11</v>
       </c>
       <c r="N67" s="3">
         <v>-18.81</v>
@@ -4352,7 +4352,7 @@
         <v>47.57</v>
       </c>
       <c r="R67" s="3">
-        <v>-18.81</v>
+        <v>92.07</v>
       </c>
       <c r="S67" t="str">
         <v/>
@@ -4384,7 +4384,7 @@
         <v>12.99</v>
       </c>
       <c r="I68" s="1">
-        <v>572122</v>
+        <v>583323</v>
       </c>
       <c r="J68" s="1">
         <v>4434.93</v>
@@ -4396,7 +4396,7 @@
         <v>4852.22</v>
       </c>
       <c r="M68" s="3">
-        <v>132.22</v>
+        <v>32.62</v>
       </c>
       <c r="N68" s="3">
         <v>-1.27</v>
@@ -4411,7 +4411,7 @@
         <v>295.92</v>
       </c>
       <c r="R68" s="3">
-        <v>-1.27</v>
+        <v>316.53</v>
       </c>
       <c r="S68" t="str">
         <v/>
@@ -4443,7 +4443,7 @@
         <v>11.83</v>
       </c>
       <c r="I69" s="1">
-        <v>3849270</v>
+        <v>3946622</v>
       </c>
       <c r="J69" s="1">
         <v>1518.4</v>
@@ -4455,7 +4455,7 @@
         <v>1579.91</v>
       </c>
       <c r="M69" s="3">
-        <v>48.99</v>
+        <v>32.59</v>
       </c>
       <c r="N69" s="3">
         <v>1.01</v>
@@ -4470,7 +4470,7 @@
         <v>54.38</v>
       </c>
       <c r="R69" s="3">
-        <v>1.01</v>
+        <v>43.62</v>
       </c>
       <c r="S69" t="str">
         <v/>
@@ -4502,7 +4502,7 @@
         <v>42.15</v>
       </c>
       <c r="I70" s="1">
-        <v>444194</v>
+        <v>448972</v>
       </c>
       <c r="J70" s="1">
         <v>7194.78</v>
@@ -4514,7 +4514,7 @@
         <v>9112.92</v>
       </c>
       <c r="M70" s="3">
-        <v>711.06</v>
+        <v>2.29</v>
       </c>
       <c r="N70" s="3">
         <v>72.61</v>
@@ -4529,7 +4529,7 @@
         <v>951.43</v>
       </c>
       <c r="R70" s="3">
-        <v>72.61</v>
+        <v>698.2</v>
       </c>
       <c r="S70" t="str">
         <v/>
@@ -4573,7 +4573,7 @@
         <v>56433.5</v>
       </c>
       <c r="M71" s="3">
-        <v>-306.23</v>
+        <v>-244.5</v>
       </c>
       <c r="N71" s="3">
         <v>-408.33</v>
@@ -4588,7 +4588,7 @@
         <v>1705.86</v>
       </c>
       <c r="R71" s="3">
-        <v>-408.33</v>
+        <v>2296.75</v>
       </c>
       <c r="S71" t="str">
         <v/>
@@ -4620,7 +4620,7 @@
         <v>18.98</v>
       </c>
       <c r="I72" s="1">
-        <v>2221593</v>
+        <v>2253293</v>
       </c>
       <c r="J72" s="1">
         <v>348.13</v>
@@ -4632,7 +4632,7 @@
         <v>398.91</v>
       </c>
       <c r="M72" s="3">
-        <v>16.88</v>
+        <v>-5.45</v>
       </c>
       <c r="N72" s="3">
         <v>-0.4</v>
@@ -4647,7 +4647,7 @@
         <v>43.66</v>
       </c>
       <c r="R72" s="3">
-        <v>-0.4</v>
+        <v>36.05</v>
       </c>
       <c r="S72" t="str">
         <v/>
@@ -4679,7 +4679,7 @@
         <v>1.65</v>
       </c>
       <c r="I73" s="1">
-        <v>406087</v>
+        <v>423330</v>
       </c>
       <c r="J73" s="1">
         <v>1823.84</v>
@@ -4691,7 +4691,7 @@
         <v>1906.43</v>
       </c>
       <c r="M73" s="3">
-        <v>25.72</v>
+        <v>-9.65</v>
       </c>
       <c r="N73" s="3">
         <v>-11.26</v>
@@ -4706,7 +4706,7 @@
         <v>136.62</v>
       </c>
       <c r="R73" s="3">
-        <v>-11.26</v>
+        <v>134.08</v>
       </c>
       <c r="S73" t="str">
         <v/>
@@ -4738,7 +4738,7 @@
         <v>-33.13</v>
       </c>
       <c r="I74" s="1">
-        <v>3971224</v>
+        <v>4011352</v>
       </c>
       <c r="J74" s="1">
         <v>437.02</v>
@@ -4750,7 +4750,7 @@
         <v>359.33</v>
       </c>
       <c r="M74" s="3">
-        <v>-25.57</v>
+        <v>0.41</v>
       </c>
       <c r="N74" s="3">
         <v>1.31</v>
@@ -4765,7 +4765,7 @@
         <v>-41.67</v>
       </c>
       <c r="R74" s="3">
-        <v>1.31</v>
+        <v>-16.52</v>
       </c>
       <c r="S74" t="str">
         <v/>
@@ -4797,7 +4797,7 @@
         <v>8.6</v>
       </c>
       <c r="I75" s="1">
-        <v>280150</v>
+        <v>285702</v>
       </c>
       <c r="J75" s="1">
         <v>2215.23</v>
@@ -4809,7 +4809,7 @@
         <v>2362.05</v>
       </c>
       <c r="M75" s="3">
-        <v>33.08</v>
+        <v>-43.73</v>
       </c>
       <c r="N75" s="3">
         <v>-32.24</v>
@@ -4824,7 +4824,7 @@
         <v>269.02</v>
       </c>
       <c r="R75" s="3">
-        <v>-32.24</v>
+        <v>282.04</v>
       </c>
       <c r="S75" t="str">
         <v/>
@@ -4856,7 +4856,7 @@
         <v>93.31</v>
       </c>
       <c r="I76" s="1">
-        <v>1919434</v>
+        <v>1929718</v>
       </c>
       <c r="J76" s="1">
         <v>1047.25</v>
@@ -4868,7 +4868,7 @@
         <v>1519.57</v>
       </c>
       <c r="M76" s="3">
-        <v>152.87</v>
+        <v>-14.08</v>
       </c>
       <c r="N76" s="3">
         <v>-16.11</v>
@@ -4883,7 +4883,7 @@
         <v>283.13</v>
       </c>
       <c r="R76" s="3">
-        <v>-16.11</v>
+        <v>197.17</v>
       </c>
       <c r="S76" t="str">
         <v/>
@@ -4915,7 +4915,7 @@
         <v>65.62</v>
       </c>
       <c r="I77" s="1">
-        <v>1409509</v>
+        <v>1426449</v>
       </c>
       <c r="J77" s="1">
         <v>629.75</v>
@@ -4927,7 +4927,7 @@
         <v>804.7</v>
       </c>
       <c r="M77" s="3">
-        <v>58.15</v>
+        <v>0.12</v>
       </c>
       <c r="N77" s="3">
         <v>2.16</v>
@@ -4942,7 +4942,7 @@
         <v>59.55</v>
       </c>
       <c r="R77" s="3">
-        <v>2.16</v>
+        <v>21.42</v>
       </c>
       <c r="S77" t="str">
         <v/>
@@ -4974,7 +4974,7 @@
         <v>-16.12</v>
       </c>
       <c r="I78" s="1">
-        <v>62333</v>
+        <v>62653</v>
       </c>
       <c r="J78" s="1">
         <v>25023.9</v>
@@ -4986,7 +4986,7 @@
         <v>23237.4</v>
       </c>
       <c r="M78" s="3">
-        <v>-939.58</v>
+        <v>-265</v>
       </c>
       <c r="N78" s="3">
         <v>-399.83</v>
@@ -5001,7 +5001,7 @@
         <v>-984.94</v>
       </c>
       <c r="R78" s="3">
-        <v>-399.83</v>
+        <v>-384.39</v>
       </c>
       <c r="S78" t="str">
         <v/>
@@ -5033,7 +5033,7 @@
         <v>-23.46</v>
       </c>
       <c r="I79" s="1">
-        <v>15143497</v>
+        <v>15572554</v>
       </c>
       <c r="J79" s="1">
         <v>1343.48</v>
@@ -5045,7 +5045,7 @@
         <v>1258.05</v>
       </c>
       <c r="M79" s="3">
-        <v>-45.11</v>
+        <v>-17.86</v>
       </c>
       <c r="N79" s="3">
         <v>-23.27</v>
@@ -5060,7 +5060,7 @@
         <v>-27.47</v>
       </c>
       <c r="R79" s="3">
-        <v>-23.27</v>
+        <v>2.75</v>
       </c>
       <c r="S79" t="str">
         <v/>
@@ -5092,7 +5092,7 @@
         <v>-14.6</v>
       </c>
       <c r="I80" s="1">
-        <v>47763</v>
+        <v>48020</v>
       </c>
       <c r="J80" s="1">
         <v>19521.29</v>
@@ -5104,7 +5104,7 @@
         <v>17564.38</v>
       </c>
       <c r="M80" s="3">
-        <v>-544.87</v>
+        <v>-20.32</v>
       </c>
       <c r="N80" s="3">
         <v>-126.63</v>
@@ -5119,7 +5119,7 @@
         <v>2506.85</v>
       </c>
       <c r="R80" s="3">
-        <v>-126.63</v>
+        <v>3170.01</v>
       </c>
       <c r="S80" t="str">
         <v/>
@@ -5151,7 +5151,7 @@
         <v>25.4</v>
       </c>
       <c r="I81" s="1">
-        <v>9648</v>
+        <v>10241</v>
       </c>
       <c r="J81" s="1">
         <v>39487.85</v>
@@ -5163,7 +5163,7 @@
         <v>46893.6</v>
       </c>
       <c r="M81" s="3">
-        <v>2134.2</v>
+        <v>-566.13</v>
       </c>
       <c r="N81" s="3">
         <v>-565.12</v>
@@ -5178,7 +5178,7 @@
         <v>4157.37</v>
       </c>
       <c r="R81" s="3">
-        <v>-565.12</v>
+        <v>3359.51</v>
       </c>
       <c r="S81" t="str">
         <v/>
@@ -5210,7 +5210,7 @@
         <v>26.74</v>
       </c>
       <c r="I82" s="1">
-        <v>1689353</v>
+        <v>1702894</v>
       </c>
       <c r="J82" s="1">
         <v>3338.4</v>
@@ -5222,7 +5222,7 @@
         <v>3314.95</v>
       </c>
       <c r="M82" s="3">
-        <v>-27.06</v>
+        <v>17.06</v>
       </c>
       <c r="N82" s="3">
         <v>-4.98</v>
@@ -5237,7 +5237,7 @@
         <v>554.15</v>
       </c>
       <c r="R82" s="3">
-        <v>-4.98</v>
+        <v>578.44</v>
       </c>
       <c r="S82" t="str">
         <v/>
@@ -5269,7 +5269,7 @@
         <v>-33.3</v>
       </c>
       <c r="I83" s="1">
-        <v>583422</v>
+        <v>598405</v>
       </c>
       <c r="J83" s="1">
         <v>629.77</v>
@@ -5281,7 +5281,7 @@
         <v>554.33</v>
       </c>
       <c r="M83" s="3">
-        <v>-31.18</v>
+        <v>-9.16</v>
       </c>
       <c r="N83" s="3">
         <v>-13.2</v>
@@ -5296,7 +5296,7 @@
         <v>-18.27</v>
       </c>
       <c r="R83" s="3">
-        <v>-13.2</v>
+        <v>-0.3</v>
       </c>
       <c r="S83" t="str">
         <v/>
@@ -5328,7 +5328,7 @@
         <v>-17.56</v>
       </c>
       <c r="I84" s="1">
-        <v>8387893</v>
+        <v>8502677</v>
       </c>
       <c r="J84" s="1">
         <v>170.36</v>
@@ -5340,7 +5340,7 @@
         <v>163.39</v>
       </c>
       <c r="M84" s="3">
-        <v>-3.67</v>
+        <v>-4.57</v>
       </c>
       <c r="N84" s="3">
         <v>-4.78</v>
@@ -5355,7 +5355,7 @@
         <v>13.8</v>
       </c>
       <c r="R84" s="3">
-        <v>-4.78</v>
+        <v>16.91</v>
       </c>
       <c r="S84" t="str">
         <v/>
@@ -5387,7 +5387,7 @@
         <v>21.82</v>
       </c>
       <c r="I85" s="1">
-        <v>245040</v>
+        <v>253448</v>
       </c>
       <c r="J85" s="1">
         <v>1022.81</v>
@@ -5399,7 +5399,7 @@
         <v>1144.69</v>
       </c>
       <c r="M85" s="3">
-        <v>33.97</v>
+        <v>-6.94</v>
       </c>
       <c r="N85" s="3">
         <v>-2.34</v>
@@ -5414,7 +5414,7 @@
         <v>72.66</v>
       </c>
       <c r="R85" s="3">
-        <v>-2.34</v>
+        <v>60.34</v>
       </c>
       <c r="S85" t="str">
         <v/>
@@ -5446,7 +5446,7 @@
         <v>1.55</v>
       </c>
       <c r="I86" s="1">
-        <v>1934540</v>
+        <v>2007016</v>
       </c>
       <c r="J86" s="1">
         <v>981.19</v>
@@ -5458,7 +5458,7 @@
         <v>987.86</v>
       </c>
       <c r="M86" s="3">
-        <v>-11.16</v>
+        <v>-26.61</v>
       </c>
       <c r="N86" s="3">
         <v>-25.75</v>
@@ -5473,7 +5473,7 @@
         <v>94.04</v>
       </c>
       <c r="R86" s="3">
-        <v>-25.75</v>
+        <v>99.03</v>
       </c>
       <c r="S86" t="str">
         <v/>
@@ -5505,7 +5505,7 @@
         <v>-3.35</v>
       </c>
       <c r="I87" s="1">
-        <v>12137590</v>
+        <v>12638617</v>
       </c>
       <c r="J87" s="1">
         <v>194.23</v>
@@ -5517,7 +5517,7 @@
         <v>183.36</v>
       </c>
       <c r="M87" s="3">
-        <v>-4.61</v>
+        <v>-3.06</v>
       </c>
       <c r="N87" s="3">
         <v>-2.73</v>
@@ -5532,7 +5532,7 @@
         <v>11.06</v>
       </c>
       <c r="R87" s="3">
-        <v>-2.73</v>
+        <v>13.67</v>
       </c>
       <c r="S87" t="str">
         <v/>
@@ -5564,7 +5564,7 @@
         <v>34.47</v>
       </c>
       <c r="I88" s="1">
-        <v>141038</v>
+        <v>143055</v>
       </c>
       <c r="J88" s="1">
         <v>3595.61</v>
@@ -5576,7 +5576,7 @@
         <v>4511.94</v>
       </c>
       <c r="M88" s="3">
-        <v>286.71</v>
+        <v>5.48</v>
       </c>
       <c r="N88" s="3">
         <v>2.92</v>
@@ -5591,7 +5591,7 @@
         <v>609.31</v>
       </c>
       <c r="R88" s="3">
-        <v>2.92</v>
+        <v>494.89</v>
       </c>
       <c r="S88" t="str">
         <v/>
@@ -5623,7 +5623,7 @@
         <v>25.3</v>
       </c>
       <c r="I89" s="1">
-        <v>377316</v>
+        <v>390489</v>
       </c>
       <c r="J89" s="1">
         <v>4118.33</v>
@@ -5635,7 +5635,7 @@
         <v>4285.59</v>
       </c>
       <c r="M89" s="3">
-        <v>-8.39</v>
+        <v>-87.81</v>
       </c>
       <c r="N89" s="3">
         <v>-55.4</v>
@@ -5650,7 +5650,7 @@
         <v>768.29</v>
       </c>
       <c r="R89" s="3">
-        <v>-55.4</v>
+        <v>777.95</v>
       </c>
       <c r="S89" t="str">
         <v/>
@@ -5682,7 +5682,7 @@
         <v>-9.28</v>
       </c>
       <c r="I90" s="1">
-        <v>1273794</v>
+        <v>1277186</v>
       </c>
       <c r="J90" s="1">
         <v>5341</v>
@@ -5694,7 +5694,7 @@
         <v>5554.21</v>
       </c>
       <c r="M90" s="3">
-        <v>111.04</v>
+        <v>91.42</v>
       </c>
       <c r="N90" s="3">
         <v>58.71</v>
@@ -5709,7 +5709,7 @@
         <v>229.25</v>
       </c>
       <c r="R90" s="3">
-        <v>58.71</v>
+        <v>311.84</v>
       </c>
       <c r="S90" t="str">
         <v/>
@@ -5741,7 +5741,7 @@
         <v>-20.72</v>
       </c>
       <c r="I91" s="1">
-        <v>260224</v>
+        <v>264019</v>
       </c>
       <c r="J91" s="1">
         <v>1811</v>
@@ -5753,7 +5753,7 @@
         <v>1818.61</v>
       </c>
       <c r="M91" s="3">
-        <v>-68.8</v>
+        <v>-64.58</v>
       </c>
       <c r="N91" s="3">
         <v>-77.89</v>
@@ -5768,7 +5768,7 @@
         <v>-115.17</v>
       </c>
       <c r="R91" s="3">
-        <v>-77.89</v>
+        <v>-82.64</v>
       </c>
       <c r="S91" t="str">
         <v/>
@@ -5800,7 +5800,7 @@
         <v>3.65</v>
       </c>
       <c r="I92" s="1">
-        <v>1260915</v>
+        <v>1297998</v>
       </c>
       <c r="J92" s="1">
         <v>800.34</v>
@@ -5812,7 +5812,7 @@
         <v>818.93</v>
       </c>
       <c r="M92" s="3">
-        <v>-2.36</v>
+        <v>-10.49</v>
       </c>
       <c r="N92" s="3">
         <v>-10.84</v>
@@ -5827,7 +5827,7 @@
         <v>50.33</v>
       </c>
       <c r="R92" s="3">
-        <v>-10.84</v>
+        <v>52.23</v>
       </c>
       <c r="S92" t="str">
         <v/>
@@ -5859,7 +5859,7 @@
         <v>56.91</v>
       </c>
       <c r="I93" s="1">
-        <v>48591</v>
+        <v>49179</v>
       </c>
       <c r="J93" s="1">
         <v>29027.28</v>
@@ -5871,7 +5871,7 @@
         <v>32166.2</v>
       </c>
       <c r="M93" s="3">
-        <v>252.49</v>
+        <v>-706.17</v>
       </c>
       <c r="N93" s="3">
         <v>-511.27</v>
@@ -5886,7 +5886,7 @@
         <v>5499.41</v>
       </c>
       <c r="R93" s="3">
-        <v>-511.27</v>
+        <v>5261.75</v>
       </c>
       <c r="S93" t="str">
         <v/>
@@ -5918,7 +5918,7 @@
         <v>-0.41</v>
       </c>
       <c r="I94" s="1">
-        <v>208753</v>
+        <v>210454</v>
       </c>
       <c r="J94" s="1">
         <v>4841.57</v>
@@ -5930,7 +5930,7 @@
         <v>4999.54</v>
       </c>
       <c r="M94" s="3">
-        <v>-84.74</v>
+        <v>-97.74</v>
       </c>
       <c r="N94" s="3">
         <v>-113.04</v>
@@ -5945,7 +5945,7 @@
         <v>420.64</v>
       </c>
       <c r="R94" s="3">
-        <v>-113.04</v>
+        <v>447.5</v>
       </c>
       <c r="S94" t="str">
         <v/>
@@ -5977,7 +5977,7 @@
         <v>1.35</v>
       </c>
       <c r="I95" s="1">
-        <v>775269</v>
+        <v>829445</v>
       </c>
       <c r="J95" s="1">
         <v>1807.61</v>
@@ -5989,7 +5989,7 @@
         <v>1861.93</v>
       </c>
       <c r="M95" s="3">
-        <v>-6.78</v>
+        <v>-33.67</v>
       </c>
       <c r="N95" s="3">
         <v>-31.57</v>
@@ -6004,7 +6004,7 @@
         <v>91.17</v>
       </c>
       <c r="R95" s="3">
-        <v>-31.57</v>
+        <v>102.26</v>
       </c>
       <c r="S95" t="str">
         <v/>
@@ -6036,7 +6036,7 @@
         <v>35.73</v>
       </c>
       <c r="I96" s="1">
-        <v>8363603</v>
+        <v>8537257</v>
       </c>
       <c r="J96" s="1">
         <v>189.91</v>
@@ -6048,7 +6048,7 @@
         <v>203.04</v>
       </c>
       <c r="M96" s="3">
-        <v>1.26</v>
+        <v>-3.39</v>
       </c>
       <c r="N96" s="3">
         <v>-3.61</v>
@@ -6063,7 +6063,7 @@
         <v>27.76</v>
       </c>
       <c r="R96" s="3">
-        <v>-3.61</v>
+        <v>25.19</v>
       </c>
       <c r="S96" t="str">
         <v/>
@@ -6095,7 +6095,7 @@
         <v>-9.13</v>
       </c>
       <c r="I97" s="1">
-        <v>93969</v>
+        <v>95218</v>
       </c>
       <c r="J97" s="1">
         <v>5464.52</v>
@@ -6107,7 +6107,7 @@
         <v>5292.97</v>
       </c>
       <c r="M97" s="3">
-        <v>-92.18</v>
+        <v>-55.78</v>
       </c>
       <c r="N97" s="3">
         <v>-34.46</v>
@@ -6122,7 +6122,7 @@
         <v>123.49</v>
       </c>
       <c r="R97" s="3">
-        <v>-34.46</v>
+        <v>213.8</v>
       </c>
       <c r="S97" t="str">
         <v/>
@@ -6154,7 +6154,7 @@
         <v>-25.1</v>
       </c>
       <c r="I98" s="1">
-        <v>370871</v>
+        <v>376832</v>
       </c>
       <c r="J98" s="1">
         <v>1313.42</v>
@@ -6166,7 +6166,7 @@
         <v>1152.98</v>
       </c>
       <c r="M98" s="3">
-        <v>-81.59</v>
+        <v>-36.61</v>
       </c>
       <c r="N98" s="3">
         <v>-37.92</v>
@@ -6181,7 +6181,7 @@
         <v>-36.56</v>
       </c>
       <c r="R98" s="3">
-        <v>-37.92</v>
+        <v>11.36</v>
       </c>
       <c r="S98" t="str">
         <v/>
@@ -6213,7 +6213,7 @@
         <v>-19.01</v>
       </c>
       <c r="I99" s="1">
-        <v>268874</v>
+        <v>269611</v>
       </c>
       <c r="J99" s="1">
         <v>3610.85</v>
@@ -6225,7 +6225,7 @@
         <v>3575.59</v>
       </c>
       <c r="M99" s="3">
-        <v>-140.12</v>
+        <v>-88.32</v>
       </c>
       <c r="N99" s="3">
         <v>-80.49</v>
@@ -6240,7 +6240,7 @@
         <v>-210.52</v>
       </c>
       <c r="R99" s="3">
-        <v>-80.49</v>
+        <v>54.65</v>
       </c>
       <c r="S99" t="str">
         <v/>
@@ -6272,7 +6272,7 @@
         <v>-30.7</v>
       </c>
       <c r="I100" s="1">
-        <v>682161</v>
+        <v>709267</v>
       </c>
       <c r="J100" s="1">
         <v>1047.9</v>
@@ -6284,7 +6284,7 @@
         <v>893.96</v>
       </c>
       <c r="M100" s="3">
-        <v>-62.44</v>
+        <v>-10.65</v>
       </c>
       <c r="N100" s="3">
         <v>-13.31</v>
@@ -6299,7 +6299,7 @@
         <v>-64.63</v>
       </c>
       <c r="R100" s="3">
-        <v>-13.31</v>
+        <v>-26.59</v>
       </c>
       <c r="S100" t="str">
         <v/>
@@ -6331,7 +6331,7 @@
         <v>2.58</v>
       </c>
       <c r="I101" s="1">
-        <v>1224854</v>
+        <v>1228705</v>
       </c>
       <c r="J101" s="1">
         <v>2305.88</v>
@@ -6343,7 +6343,7 @@
         <v>2388.57</v>
       </c>
       <c r="M101" s="3">
-        <v>2.27</v>
+        <v>-25.03</v>
       </c>
       <c r="N101" s="3">
         <v>-1.18</v>
@@ -6358,7 +6358,7 @@
         <v>58.02</v>
       </c>
       <c r="R101" s="3">
-        <v>-1.18</v>
+        <v>71.94</v>
       </c>
       <c r="S101" t="str">
         <v/>
@@ -6390,7 +6390,7 @@
         <v>-35.29</v>
       </c>
       <c r="I102" s="1">
-        <v>11225881</v>
+        <v>11528925</v>
       </c>
       <c r="J102" s="1">
         <v>296.05</v>
@@ -6402,7 +6402,7 @@
         <v>266.62</v>
       </c>
       <c r="M102" s="3">
-        <v>-13.73</v>
+        <v>-1.43</v>
       </c>
       <c r="N102" s="3">
         <v>-1.58</v>
@@ -6417,7 +6417,7 @@
         <v>-41.18</v>
       </c>
       <c r="R102" s="3">
-        <v>-1.58</v>
+        <v>-29.53</v>
       </c>
       <c r="S102" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>-0.76</v>
       </c>
       <c r="I103" s="1">
-        <v>8540</v>
+        <v>8744</v>
       </c>
       <c r="J103" s="1">
         <v>36383.5</v>
@@ -6461,7 +6461,7 @@
         <v>36461.6</v>
       </c>
       <c r="M103" s="3">
-        <v>-407.15</v>
+        <v>-69.37</v>
       </c>
       <c r="N103" s="3">
         <v>49.39</v>
@@ -6476,7 +6476,7 @@
         <v>-1209.01</v>
       </c>
       <c r="R103" s="3">
-        <v>49.39</v>
+        <v>-909.08</v>
       </c>
       <c r="S103" t="str">
         <v/>
@@ -6508,7 +6508,7 @@
         <v>61.63</v>
       </c>
       <c r="I104" s="1">
-        <v>89688</v>
+        <v>91543</v>
       </c>
       <c r="J104" s="1">
         <v>16643.19</v>
@@ -6520,7 +6520,7 @@
         <v>20023.82</v>
       </c>
       <c r="M104" s="3">
-        <v>1065.66</v>
+        <v>13.09</v>
       </c>
       <c r="N104" s="3">
         <v>-14.58</v>
@@ -6535,7 +6535,7 @@
         <v>2614.56</v>
       </c>
       <c r="R104" s="3">
-        <v>-14.58</v>
+        <v>2236.11</v>
       </c>
       <c r="S104" t="str">
         <v/>
@@ -6567,7 +6567,7 @@
         <v>-27.45</v>
       </c>
       <c r="I105" s="1">
-        <v>8964658</v>
+        <v>9223615</v>
       </c>
       <c r="J105" s="1">
         <v>244.87</v>
@@ -6579,7 +6579,7 @@
         <v>231.99</v>
       </c>
       <c r="M105" s="3">
-        <v>-9.62</v>
+        <v>-4.5</v>
       </c>
       <c r="N105" s="3">
         <v>-5.18</v>
@@ -6594,7 +6594,7 @@
         <v>-15.2</v>
       </c>
       <c r="R105" s="3">
-        <v>-5.18</v>
+        <v>-8.34</v>
       </c>
       <c r="S105" t="str">
         <v/>
@@ -6626,7 +6626,7 @@
         <v>-10.75</v>
       </c>
       <c r="I106" s="1">
-        <v>8647484</v>
+        <v>8894570</v>
       </c>
       <c r="J106" s="1">
         <v>77.44</v>
@@ -6638,7 +6638,7 @@
         <v>75.25</v>
       </c>
       <c r="M106" s="3">
-        <v>-1.67</v>
+        <v>-1.07</v>
       </c>
       <c r="N106" s="3">
         <v>-0.96</v>
@@ -6653,7 +6653,7 @@
         <v>-0.08</v>
       </c>
       <c r="R106" s="3">
-        <v>-0.96</v>
+        <v>1.71</v>
       </c>
       <c r="S106" t="str">
         <v/>
@@ -6685,7 +6685,7 @@
         <v>-25.98</v>
       </c>
       <c r="I107" s="1">
-        <v>793064</v>
+        <v>795567</v>
       </c>
       <c r="J107" s="1">
         <v>471.4</v>
@@ -6697,7 +6697,7 @@
         <v>474.22</v>
       </c>
       <c r="M107" s="3">
-        <v>-11.91</v>
+        <v>-16.36</v>
       </c>
       <c r="N107" s="3">
         <v>-13.13</v>
@@ -6712,7 +6712,7 @@
         <v>-42.42</v>
       </c>
       <c r="R107" s="3">
-        <v>-13.13</v>
+        <v>-27.78</v>
       </c>
       <c r="S107" t="str">
         <v/>
@@ -6744,7 +6744,7 @@
         <v>-23.38</v>
       </c>
       <c r="I108" s="1">
-        <v>906802</v>
+        <v>911205</v>
       </c>
       <c r="J108" s="1">
         <v>1599.61</v>
@@ -6756,7 +6756,7 @@
         <v>1472.28</v>
       </c>
       <c r="M108" s="3">
-        <v>-74.63</v>
+        <v>-58.95</v>
       </c>
       <c r="N108" s="3">
         <v>-53.36</v>
@@ -6771,7 +6771,7 @@
         <v>77.76</v>
       </c>
       <c r="R108" s="3">
-        <v>-53.36</v>
+        <v>132.33</v>
       </c>
       <c r="S108" t="str">
         <v/>
@@ -6815,7 +6815,7 @@
         <v>23514.27</v>
       </c>
       <c r="M109" s="3">
-        <v>-378</v>
+        <v>-185.04</v>
       </c>
       <c r="N109" s="3">
         <v>-273.79</v>
@@ -6830,7 +6830,7 @@
         <v>200.23</v>
       </c>
       <c r="R109" s="3">
-        <v>-273.79</v>
+        <v>600.9</v>
       </c>
       <c r="S109" t="str">
         <v/>
@@ -6862,7 +6862,7 @@
         <v>-7.98</v>
       </c>
       <c r="I110" s="1">
-        <v>5668967</v>
+        <v>5725234</v>
       </c>
       <c r="J110" s="1">
         <v>411.19</v>
@@ -6874,7 +6874,7 @@
         <v>404.4</v>
       </c>
       <c r="M110" s="3">
-        <v>-5.33</v>
+        <v>-3.44</v>
       </c>
       <c r="N110" s="3">
         <v>-4.47</v>
@@ -6889,7 +6889,7 @@
         <v>-6.83</v>
       </c>
       <c r="R110" s="3">
-        <v>-4.47</v>
+        <v>-2.5</v>
       </c>
       <c r="S110" t="str">
         <v/>
@@ -6921,7 +6921,7 @@
         <v>10.1</v>
       </c>
       <c r="I111" s="1">
-        <v>105397</v>
+        <v>110832</v>
       </c>
       <c r="J111" s="1">
         <v>10259.47</v>
@@ -6933,7 +6933,7 @@
         <v>11267.96</v>
       </c>
       <c r="M111" s="3">
-        <v>131.51</v>
+        <v>-317.93</v>
       </c>
       <c r="N111" s="3">
         <v>-359.58</v>
@@ -6948,7 +6948,7 @@
         <v>834.56</v>
       </c>
       <c r="R111" s="3">
-        <v>-359.58</v>
+        <v>772.15</v>
       </c>
       <c r="S111" t="str">
         <v/>
@@ -6980,7 +6980,7 @@
         <v>-12.64</v>
       </c>
       <c r="I112" s="1">
-        <v>414485</v>
+        <v>421181</v>
       </c>
       <c r="J112" s="1">
         <v>3976.59</v>
@@ -6992,7 +6992,7 @@
         <v>3761.82</v>
       </c>
       <c r="M112" s="3">
-        <v>-165.8</v>
+        <v>-124.24</v>
       </c>
       <c r="N112" s="3">
         <v>-94.15</v>
@@ -7007,7 +7007,7 @@
         <v>-80.11</v>
       </c>
       <c r="R112" s="3">
-        <v>-94.15</v>
+        <v>-6.94</v>
       </c>
       <c r="S112" t="str">
         <v/>
@@ -7039,7 +7039,7 @@
         <v>-8.07</v>
       </c>
       <c r="I113" s="1">
-        <v>591569</v>
+        <v>602008</v>
       </c>
       <c r="J113" s="1">
         <v>2249.35</v>
@@ -7051,7 +7051,7 @@
         <v>2112.34</v>
       </c>
       <c r="M113" s="3">
-        <v>-81.27</v>
+        <v>-50.69</v>
       </c>
       <c r="N113" s="3">
         <v>-50.82</v>
@@ -7066,7 +7066,7 @@
         <v>121.65</v>
       </c>
       <c r="R113" s="3">
-        <v>-50.82</v>
+        <v>171.74</v>
       </c>
       <c r="S113" t="str">
         <v/>
@@ -7098,7 +7098,7 @@
         <v>-7.51</v>
       </c>
       <c r="I114" s="1">
-        <v>281443</v>
+        <v>287546</v>
       </c>
       <c r="J114" s="1">
         <v>1477.26</v>
@@ -7110,7 +7110,7 @@
         <v>1525.44</v>
       </c>
       <c r="M114" s="3">
-        <v>-4.81</v>
+        <v>-13.34</v>
       </c>
       <c r="N114" s="3">
         <v>-22.74</v>
@@ -7125,7 +7125,7 @@
         <v>61.76</v>
       </c>
       <c r="R114" s="3">
-        <v>-22.74</v>
+        <v>83.42</v>
       </c>
       <c r="S114" t="str">
         <v/>
@@ -7157,7 +7157,7 @@
         <v>0.47</v>
       </c>
       <c r="I115" s="1">
-        <v>14546344</v>
+        <v>15004260</v>
       </c>
       <c r="J115" s="1">
         <v>400.21</v>
@@ -7169,7 +7169,7 @@
         <v>415.25</v>
       </c>
       <c r="M115" s="3">
-        <v>11.05</v>
+        <v>9.16</v>
       </c>
       <c r="N115" s="3">
         <v>7.4</v>
@@ -7184,7 +7184,7 @@
         <v>9.8</v>
       </c>
       <c r="R115" s="3">
-        <v>7.4</v>
+        <v>8.39</v>
       </c>
       <c r="S115" t="str">
         <v/>
@@ -7216,7 +7216,7 @@
         <v>2.84</v>
       </c>
       <c r="I116" s="1">
-        <v>24716133</v>
+        <v>25149396</v>
       </c>
       <c r="J116" s="1">
         <v>1353.47</v>
@@ -7228,7 +7228,7 @@
         <v>1382.69</v>
       </c>
       <c r="M116" s="3">
-        <v>5.38</v>
+        <v>0.12</v>
       </c>
       <c r="N116" s="3">
         <v>-9.21</v>
@@ -7243,7 +7243,7 @@
         <v>51.43</v>
       </c>
       <c r="R116" s="3">
-        <v>-9.21</v>
+        <v>62.95</v>
       </c>
       <c r="S116" t="str">
         <v/>
@@ -7275,7 +7275,7 @@
         <v>-5.52</v>
       </c>
       <c r="I117" s="1">
-        <v>309153</v>
+        <v>317558</v>
       </c>
       <c r="J117" s="1">
         <v>1370.71</v>
@@ -7287,7 +7287,7 @@
         <v>1441.19</v>
       </c>
       <c r="M117" s="3">
-        <v>4.3</v>
+        <v>-17.03</v>
       </c>
       <c r="N117" s="3">
         <v>-22.33</v>
@@ -7302,7 +7302,7 @@
         <v>35.03</v>
       </c>
       <c r="R117" s="3">
-        <v>-22.33</v>
+        <v>47.73</v>
       </c>
       <c r="S117" t="str">
         <v/>
@@ -7334,7 +7334,7 @@
         <v>14.95</v>
       </c>
       <c r="I118" s="1">
-        <v>4197589</v>
+        <v>4231992</v>
       </c>
       <c r="J118" s="1">
         <v>170.38</v>
@@ -7346,7 +7346,7 @@
         <v>179.41</v>
       </c>
       <c r="M118" s="3">
-        <v>1.83</v>
+        <v>-3.04</v>
       </c>
       <c r="N118" s="3">
         <v>-2.38</v>
@@ -7361,7 +7361,7 @@
         <v>16.79</v>
       </c>
       <c r="R118" s="3">
-        <v>-2.38</v>
+        <v>15.14</v>
       </c>
       <c r="S118" t="str">
         <v/>
@@ -7393,7 +7393,7 @@
         <v>31.86</v>
       </c>
       <c r="I119" s="1">
-        <v>8834317</v>
+        <v>9408721</v>
       </c>
       <c r="J119" s="1">
         <v>138.07</v>
@@ -7405,7 +7405,7 @@
         <v>163.34</v>
       </c>
       <c r="M119" s="3">
-        <v>7.48</v>
+        <v>-0.85</v>
       </c>
       <c r="N119" s="3">
         <v>-0.99</v>
@@ -7420,7 +7420,7 @@
         <v>17.74</v>
       </c>
       <c r="R119" s="3">
-        <v>-0.99</v>
+        <v>13.48</v>
       </c>
       <c r="S119" t="str">
         <v/>
@@ -7452,7 +7452,7 @@
         <v>11.22</v>
       </c>
       <c r="I120" s="1">
-        <v>5297317</v>
+        <v>5411850</v>
       </c>
       <c r="J120" s="1">
         <v>269.17</v>
@@ -7464,7 +7464,7 @@
         <v>266.31</v>
       </c>
       <c r="M120" s="3">
-        <v>-3.3</v>
+        <v>-5.18</v>
       </c>
       <c r="N120" s="3">
         <v>-3.76</v>
@@ -7479,7 +7479,7 @@
         <v>33.82</v>
       </c>
       <c r="R120" s="3">
-        <v>-3.76</v>
+        <v>33.76</v>
       </c>
       <c r="S120" t="str">
         <v/>
@@ -7511,7 +7511,7 @@
         <v>13.59</v>
       </c>
       <c r="I121" s="1">
-        <v>2281148</v>
+        <v>2293449</v>
       </c>
       <c r="J121" s="1">
         <v>464.77</v>
@@ -7523,7 +7523,7 @@
         <v>585.91</v>
       </c>
       <c r="M121" s="3">
-        <v>32.01</v>
+        <v>-7</v>
       </c>
       <c r="N121" s="3">
         <v>-7.27</v>
@@ -7538,7 +7538,7 @@
         <v>25.69</v>
       </c>
       <c r="R121" s="3">
-        <v>-7.27</v>
+        <v>20.58</v>
       </c>
       <c r="S121" t="str">
         <v/>
@@ -7570,7 +7570,7 @@
         <v>-33.19</v>
       </c>
       <c r="I122" s="1">
-        <v>323580</v>
+        <v>325681</v>
       </c>
       <c r="J122" s="1">
         <v>2804.33</v>
@@ -7582,7 +7582,7 @@
         <v>2373.54</v>
       </c>
       <c r="M122" s="3">
-        <v>-208.01</v>
+        <v>-63.72</v>
       </c>
       <c r="N122" s="3">
         <v>-67.19</v>
@@ -7597,7 +7597,7 @@
         <v>-339.74</v>
       </c>
       <c r="R122" s="3">
-        <v>-67.19</v>
+        <v>-214.27</v>
       </c>
       <c r="S122" t="str">
         <v/>
@@ -7629,7 +7629,7 @@
         <v>-30.82</v>
       </c>
       <c r="I123" s="1">
-        <v>15323378</v>
+        <v>15779196</v>
       </c>
       <c r="J123" s="1">
         <v>196.45</v>
@@ -7641,7 +7641,7 @@
         <v>172.46</v>
       </c>
       <c r="M123" s="3">
-        <v>-8.15</v>
+        <v>1.66</v>
       </c>
       <c r="N123" s="3">
         <v>-1.43</v>
@@ -7656,7 +7656,7 @@
         <v>-19.32</v>
       </c>
       <c r="R123" s="3">
-        <v>-1.43</v>
+        <v>-12.4</v>
       </c>
       <c r="S123" t="str">
         <v/>
@@ -7688,7 +7688,7 @@
         <v>-21.99</v>
       </c>
       <c r="I124" s="1">
-        <v>126790</v>
+        <v>130763</v>
       </c>
       <c r="J124" s="1">
         <v>5493.31</v>
@@ -7700,7 +7700,7 @@
         <v>5106.93</v>
       </c>
       <c r="M124" s="3">
-        <v>-207.03</v>
+        <v>-83.67</v>
       </c>
       <c r="N124" s="3">
         <v>-92.45</v>
@@ -7715,7 +7715,7 @@
         <v>-35.75</v>
       </c>
       <c r="R124" s="3">
-        <v>-92.45</v>
+        <v>113.72</v>
       </c>
       <c r="S124" t="str">
         <v/>
@@ -7747,7 +7747,7 @@
         <v>-32.68</v>
       </c>
       <c r="I125" s="1">
-        <v>351119</v>
+        <v>354302</v>
       </c>
       <c r="J125" s="1">
         <v>3248.13</v>
@@ -7759,7 +7759,7 @@
         <v>2834.12</v>
       </c>
       <c r="M125" s="3">
-        <v>-167.78</v>
+        <v>-76.66</v>
       </c>
       <c r="N125" s="3">
         <v>-72.19</v>
@@ -7774,7 +7774,7 @@
         <v>231.99</v>
       </c>
       <c r="R125" s="3">
-        <v>-72.19</v>
+        <v>363.1</v>
       </c>
       <c r="S125" t="str">
         <v/>
@@ -7806,7 +7806,7 @@
         <v>-16.99</v>
       </c>
       <c r="I126" s="1">
-        <v>189895</v>
+        <v>193264</v>
       </c>
       <c r="J126" s="1">
         <v>2719.44</v>
@@ -7818,7 +7818,7 @@
         <v>2599.5</v>
       </c>
       <c r="M126" s="3">
-        <v>-158.68</v>
+        <v>-125.05</v>
       </c>
       <c r="N126" s="3">
         <v>-117.75</v>
@@ -7833,7 +7833,7 @@
         <v>-159.88</v>
       </c>
       <c r="R126" s="3">
-        <v>-117.75</v>
+        <v>-99.98</v>
       </c>
       <c r="S126" t="str">
         <v/>
@@ -7865,7 +7865,7 @@
         <v>-18.92</v>
       </c>
       <c r="I127" s="1">
-        <v>509914</v>
+        <v>546793</v>
       </c>
       <c r="J127" s="1">
         <v>1102.21</v>
@@ -7877,7 +7877,7 @@
         <v>1012.37</v>
       </c>
       <c r="M127" s="3">
-        <v>-42.69</v>
+        <v>-10.56</v>
       </c>
       <c r="N127" s="3">
         <v>-15.1</v>
@@ -7892,7 +7892,7 @@
         <v>0.84</v>
       </c>
       <c r="R127" s="3">
-        <v>-15.1</v>
+        <v>27.49</v>
       </c>
       <c r="S127" t="str">
         <v/>
@@ -7924,7 +7924,7 @@
         <v>18.65</v>
       </c>
       <c r="I128" s="1">
-        <v>841637</v>
+        <v>854302</v>
       </c>
       <c r="J128" s="1">
         <v>2592.28</v>
@@ -7936,7 +7936,7 @@
         <v>2920.84</v>
       </c>
       <c r="M128" s="3">
-        <v>39.7</v>
+        <v>-80.91</v>
       </c>
       <c r="N128" s="3">
         <v>-72.88</v>
@@ -7951,7 +7951,7 @@
         <v>76.86</v>
       </c>
       <c r="R128" s="3">
-        <v>-72.88</v>
+        <v>16.9</v>
       </c>
       <c r="S128" t="str">
         <v/>
@@ -7983,7 +7983,7 @@
         <v>-12.03</v>
       </c>
       <c r="I129" s="1">
-        <v>553044</v>
+        <v>555214</v>
       </c>
       <c r="J129" s="1">
         <v>1312.19</v>
@@ -7995,7 +7995,7 @@
         <v>1335.81</v>
       </c>
       <c r="M129" s="3">
-        <v>-12.33</v>
+        <v>-17.83</v>
       </c>
       <c r="N129" s="3">
         <v>-21.43</v>
@@ -8010,7 +8010,7 @@
         <v>30.76</v>
       </c>
       <c r="R129" s="3">
-        <v>-21.43</v>
+        <v>66.22</v>
       </c>
       <c r="S129" t="str">
         <v/>
@@ -8042,7 +8042,7 @@
         <v>3.18</v>
       </c>
       <c r="I130" s="1">
-        <v>2966960</v>
+        <v>3094405</v>
       </c>
       <c r="J130" s="1">
         <v>434.03</v>
@@ -8054,7 +8054,7 @@
         <v>414.33</v>
       </c>
       <c r="M130" s="3">
-        <v>-5.23</v>
+        <v>-1.28</v>
       </c>
       <c r="N130" s="3">
         <v>-0.79</v>
@@ -8069,7 +8069,7 @@
         <v>13.37</v>
       </c>
       <c r="R130" s="3">
-        <v>-0.79</v>
+        <v>18.08</v>
       </c>
       <c r="S130" t="str">
         <v/>
@@ -8101,7 +8101,7 @@
         <v>0.01</v>
       </c>
       <c r="I131" s="1">
-        <v>399562</v>
+        <v>413687</v>
       </c>
       <c r="J131" s="1">
         <v>1500.61</v>
@@ -8113,7 +8113,7 @@
         <v>1580.81</v>
       </c>
       <c r="M131" s="3">
-        <v>1.41</v>
+        <v>-23.12</v>
       </c>
       <c r="N131" s="3">
         <v>-28.11</v>
@@ -8128,7 +8128,7 @@
         <v>31.71</v>
       </c>
       <c r="R131" s="3">
-        <v>-28.11</v>
+        <v>31.13</v>
       </c>
       <c r="S131" t="str">
         <v/>
@@ -8160,7 +8160,7 @@
         <v>-8.77</v>
       </c>
       <c r="I132" s="1">
-        <v>556277</v>
+        <v>573647</v>
       </c>
       <c r="J132" s="1">
         <v>1676.36</v>
@@ -8172,7 +8172,7 @@
         <v>1763.03</v>
       </c>
       <c r="M132" s="3">
-        <v>-12.13</v>
+        <v>-56.74</v>
       </c>
       <c r="N132" s="3">
         <v>-58.66</v>
@@ -8187,7 +8187,7 @@
         <v>105.72</v>
       </c>
       <c r="R132" s="3">
-        <v>-58.66</v>
+        <v>124.78</v>
       </c>
       <c r="S132" t="str">
         <v/>
@@ -8219,7 +8219,7 @@
         <v>-27.25</v>
       </c>
       <c r="I133" s="1">
-        <v>1477817</v>
+        <v>1519939</v>
       </c>
       <c r="J133" s="1">
         <v>610.6</v>
@@ -8231,7 +8231,7 @@
         <v>541.22</v>
       </c>
       <c r="M133" s="3">
-        <v>-21.54</v>
+        <v>2.9</v>
       </c>
       <c r="N133" s="3">
         <v>1.89</v>
@@ -8246,7 +8246,7 @@
         <v>-34.68</v>
       </c>
       <c r="R133" s="3">
-        <v>1.89</v>
+        <v>-11.46</v>
       </c>
       <c r="S133" t="str">
         <v/>
@@ -8278,7 +8278,7 @@
         <v>3.57</v>
       </c>
       <c r="I134" s="1">
-        <v>1881995</v>
+        <v>1895664</v>
       </c>
       <c r="J134" s="1">
         <v>311.1</v>
@@ -8290,7 +8290,7 @@
         <v>332.8</v>
       </c>
       <c r="M134" s="3">
-        <v>4.25</v>
+        <v>-2.38</v>
       </c>
       <c r="N134" s="3">
         <v>-4.46</v>
@@ -8305,7 +8305,7 @@
         <v>35.1</v>
       </c>
       <c r="R134" s="3">
-        <v>-4.46</v>
+        <v>34.26</v>
       </c>
       <c r="S134" t="str">
         <v/>
@@ -8337,7 +8337,7 @@
         <v>15.75</v>
       </c>
       <c r="I135" s="1">
-        <v>1287427</v>
+        <v>1309638</v>
       </c>
       <c r="J135" s="1">
         <v>1528.08</v>
@@ -8349,7 +8349,7 @@
         <v>1856.12</v>
       </c>
       <c r="M135" s="3">
-        <v>119.94</v>
+        <v>28.65</v>
       </c>
       <c r="N135" s="3">
         <v>14.34</v>
@@ -8364,7 +8364,7 @@
         <v>104.95</v>
       </c>
       <c r="R135" s="3">
-        <v>14.34</v>
+        <v>85.24</v>
       </c>
       <c r="S135" t="str">
         <v/>
@@ -8396,7 +8396,7 @@
         <v>1.77</v>
       </c>
       <c r="I136" s="1">
-        <v>293900</v>
+        <v>308699</v>
       </c>
       <c r="J136" s="1">
         <v>2979.75</v>
@@ -8408,7 +8408,7 @@
         <v>3171.52</v>
       </c>
       <c r="M136" s="3">
-        <v>6.67</v>
+        <v>-88.23</v>
       </c>
       <c r="N136" s="3">
         <v>-84.64</v>
@@ -8423,7 +8423,7 @@
         <v>185.62</v>
       </c>
       <c r="R136" s="3">
-        <v>-84.64</v>
+        <v>191.61</v>
       </c>
       <c r="S136" t="str">
         <v/>
@@ -8455,7 +8455,7 @@
         <v>-15.87</v>
       </c>
       <c r="I137" s="1">
-        <v>400597</v>
+        <v>406198</v>
       </c>
       <c r="J137" s="1">
         <v>489.27</v>
@@ -8467,7 +8467,7 @@
         <v>485.73</v>
       </c>
       <c r="M137" s="3">
-        <v>-11.51</v>
+        <v>-11.94</v>
       </c>
       <c r="N137" s="3">
         <v>-13.77</v>
@@ -8482,7 +8482,7 @@
         <v>-39.4</v>
       </c>
       <c r="R137" s="3">
-        <v>-13.77</v>
+        <v>-35.42</v>
       </c>
       <c r="S137" t="str">
         <v/>
@@ -8514,7 +8514,7 @@
         <v>-7</v>
       </c>
       <c r="I138" s="1">
-        <v>3317846</v>
+        <v>3408806</v>
       </c>
       <c r="J138" s="1">
         <v>1008.7</v>
@@ -8526,7 +8526,7 @@
         <v>1032.93</v>
       </c>
       <c r="M138" s="3">
-        <v>-5.25</v>
+        <v>-24.6</v>
       </c>
       <c r="N138" s="3">
         <v>-25.42</v>
@@ -8541,7 +8541,7 @@
         <v>124.04</v>
       </c>
       <c r="R138" s="3">
-        <v>-25.42</v>
+        <v>126.73</v>
       </c>
       <c r="S138" t="str">
         <v/>
@@ -8573,7 +8573,7 @@
         <v>-27.68</v>
       </c>
       <c r="I139" s="1">
-        <v>475748</v>
+        <v>477758</v>
       </c>
       <c r="J139" s="1">
         <v>4184.81</v>
@@ -8585,7 +8585,7 @@
         <v>3474.41</v>
       </c>
       <c r="M139" s="3">
-        <v>-239.8</v>
+        <v>69.44</v>
       </c>
       <c r="N139" s="3">
         <v>-27.72</v>
@@ -8600,7 +8600,7 @@
         <v>-786</v>
       </c>
       <c r="R139" s="3">
-        <v>-27.72</v>
+        <v>-673.44</v>
       </c>
       <c r="S139" t="str">
         <v/>
@@ -8632,7 +8632,7 @@
         <v>-10.94</v>
       </c>
       <c r="I140" s="1">
-        <v>8336142</v>
+        <v>8586339</v>
       </c>
       <c r="J140" s="1">
         <v>1895.53</v>
@@ -8644,7 +8644,7 @@
         <v>1858.82</v>
       </c>
       <c r="M140" s="3">
-        <v>-16.48</v>
+        <v>1.55</v>
       </c>
       <c r="N140" s="3">
         <v>-12.86</v>
@@ -8659,7 +8659,7 @@
         <v>102.71</v>
       </c>
       <c r="R140" s="3">
-        <v>-12.86</v>
+        <v>149.06</v>
       </c>
       <c r="S140" t="str">
         <v/>
@@ -8691,7 +8691,7 @@
         <v>0.35</v>
       </c>
       <c r="I141" s="1">
-        <v>252809</v>
+        <v>256418</v>
       </c>
       <c r="J141" s="1">
         <v>1686.58</v>
@@ -8703,7 +8703,7 @@
         <v>1802.28</v>
       </c>
       <c r="M141" s="3">
-        <v>10.33</v>
+        <v>-32.79</v>
       </c>
       <c r="N141" s="3">
         <v>-28.6</v>
@@ -8718,7 +8718,7 @@
         <v>58.6</v>
       </c>
       <c r="R141" s="3">
-        <v>-28.6</v>
+        <v>64.01</v>
       </c>
       <c r="S141" t="str">
         <v/>
@@ -8750,7 +8750,7 @@
         <v>-0.12</v>
       </c>
       <c r="I142" s="1">
-        <v>1267714</v>
+        <v>1283832</v>
       </c>
       <c r="J142" s="1">
         <v>924.48</v>
@@ -8762,7 +8762,7 @@
         <v>958.08</v>
       </c>
       <c r="M142" s="3">
-        <v>-6.81</v>
+        <v>-26.58</v>
       </c>
       <c r="N142" s="3">
         <v>-28.16</v>
@@ -8777,7 +8777,7 @@
         <v>-44.91</v>
       </c>
       <c r="R142" s="3">
-        <v>-28.16</v>
+        <v>-66.33</v>
       </c>
       <c r="S142" t="str">
         <v/>
@@ -8809,7 +8809,7 @@
         <v>2.86</v>
       </c>
       <c r="I143" s="1">
-        <v>3677121</v>
+        <v>3712637</v>
       </c>
       <c r="J143" s="1">
         <v>688.87</v>
@@ -8821,7 +8821,7 @@
         <v>726.12</v>
       </c>
       <c r="M143" s="3">
-        <v>15.37</v>
+        <v>5.99</v>
       </c>
       <c r="N143" s="3">
         <v>1.47</v>
@@ -8836,7 +8836,7 @@
         <v>31.51</v>
       </c>
       <c r="R143" s="3">
-        <v>1.47</v>
+        <v>37.29</v>
       </c>
       <c r="S143" t="str">
         <v/>
@@ -8868,7 +8868,7 @@
         <v>-34.46</v>
       </c>
       <c r="I144" s="1">
-        <v>990155</v>
+        <v>1000580</v>
       </c>
       <c r="J144" s="1">
         <v>543.1</v>
@@ -8880,7 +8880,7 @@
         <v>480.38</v>
       </c>
       <c r="M144" s="3">
-        <v>-26.23</v>
+        <v>-10.09</v>
       </c>
       <c r="N144" s="3">
         <v>-9.63</v>
@@ -8895,7 +8895,7 @@
         <v>-35.68</v>
       </c>
       <c r="R144" s="3">
-        <v>-9.63</v>
+        <v>-16.57</v>
       </c>
       <c r="S144" t="str">
         <v/>
@@ -8927,7 +8927,7 @@
         <v>15.16</v>
       </c>
       <c r="I145" s="1">
-        <v>16978492</v>
+        <v>17850721</v>
       </c>
       <c r="J145" s="1">
         <v>278.62</v>
@@ -8939,7 +8939,7 @@
         <v>323.96</v>
       </c>
       <c r="M145" s="3">
-        <v>15.36</v>
+        <v>-0.61</v>
       </c>
       <c r="N145" s="3">
         <v>0.17</v>
@@ -8954,7 +8954,7 @@
         <v>26.89</v>
       </c>
       <c r="R145" s="3">
-        <v>0.17</v>
+        <v>26.34</v>
       </c>
       <c r="S145" t="str">
         <v/>
@@ -8986,7 +8986,7 @@
         <v>-14.93</v>
       </c>
       <c r="I146" s="1">
-        <v>484049</v>
+        <v>487177</v>
       </c>
       <c r="J146" s="1">
         <v>2044.77</v>
@@ -8998,7 +8998,7 @@
         <v>2127.31</v>
       </c>
       <c r="M146" s="3">
-        <v>-4.35</v>
+        <v>-48.28</v>
       </c>
       <c r="N146" s="3">
         <v>-49.18</v>
@@ -9013,7 +9013,7 @@
         <v>26.5</v>
       </c>
       <c r="R146" s="3">
-        <v>-49.18</v>
+        <v>50.23</v>
       </c>
       <c r="S146" t="str">
         <v/>
@@ -9045,7 +9045,7 @@
         <v>-20.91</v>
       </c>
       <c r="I147" s="1">
-        <v>209679</v>
+        <v>215333</v>
       </c>
       <c r="J147" s="1">
         <v>2662.91</v>
@@ -9057,7 +9057,7 @@
         <v>2536.62</v>
       </c>
       <c r="M147" s="3">
-        <v>-63.84</v>
+        <v>-20.16</v>
       </c>
       <c r="N147" s="3">
         <v>-20.85</v>
@@ -9072,7 +9072,7 @@
         <v>-13.36</v>
       </c>
       <c r="R147" s="3">
-        <v>-20.85</v>
+        <v>45.92</v>
       </c>
       <c r="S147" t="str">
         <v/>
@@ -9104,7 +9104,7 @@
         <v>-22.61</v>
       </c>
       <c r="I148" s="1">
-        <v>307378</v>
+        <v>314312</v>
       </c>
       <c r="J148" s="1">
         <v>1247.77</v>
@@ -9116,7 +9116,7 @@
         <v>1158.15</v>
       </c>
       <c r="M148" s="3">
-        <v>-51.21</v>
+        <v>-11.69</v>
       </c>
       <c r="N148" s="3">
         <v>-24.86</v>
@@ -9131,7 +9131,7 @@
         <v>-101.7</v>
       </c>
       <c r="R148" s="3">
-        <v>-24.86</v>
+        <v>-65.83</v>
       </c>
       <c r="S148" t="str">
         <v/>
@@ -9163,7 +9163,7 @@
         <v>-19.36</v>
       </c>
       <c r="I149" s="1">
-        <v>383311</v>
+        <v>384352</v>
       </c>
       <c r="J149" s="1">
         <v>928.11</v>
@@ -9175,7 +9175,7 @@
         <v>910.49</v>
       </c>
       <c r="M149" s="3">
-        <v>-16.81</v>
+        <v>-8.02</v>
       </c>
       <c r="N149" s="3">
         <v>-12.95</v>
@@ -9190,7 +9190,7 @@
         <v>8.02</v>
       </c>
       <c r="R149" s="3">
-        <v>-12.95</v>
+        <v>43.79</v>
       </c>
       <c r="S149" t="str">
         <v/>
@@ -9222,7 +9222,7 @@
         <v>-30.75</v>
       </c>
       <c r="I150" s="1">
-        <v>5329662</v>
+        <v>5406486</v>
       </c>
       <c r="J150" s="1">
         <v>114.82</v>
@@ -9234,7 +9234,7 @@
         <v>103.49</v>
       </c>
       <c r="M150" s="3">
-        <v>-5.99</v>
+        <v>-2.48</v>
       </c>
       <c r="N150" s="3">
         <v>-2.17</v>
@@ -9249,7 +9249,7 @@
         <v>-2.93</v>
       </c>
       <c r="R150" s="3">
-        <v>-2.17</v>
+        <v>1.33</v>
       </c>
       <c r="S150" t="str">
         <v/>
@@ -9281,7 +9281,7 @@
         <v>32.87</v>
       </c>
       <c r="I151" s="1">
-        <v>118738</v>
+        <v>119668</v>
       </c>
       <c r="J151" s="1">
         <v>9371.02</v>
@@ -9293,7 +9293,7 @@
         <v>11328.4</v>
       </c>
       <c r="M151" s="3">
-        <v>372.21</v>
+        <v>-292.72</v>
       </c>
       <c r="N151" s="3">
         <v>-294.38</v>
@@ -9308,7 +9308,7 @@
         <v>843.75</v>
       </c>
       <c r="R151" s="3">
-        <v>-294.38</v>
+        <v>671.76</v>
       </c>
       <c r="S151" t="str">
         <v/>
@@ -9340,7 +9340,7 @@
         <v>-15.23</v>
       </c>
       <c r="I152" s="1">
-        <v>9640698</v>
+        <v>9863444</v>
       </c>
       <c r="J152" s="1">
         <v>83.55</v>
@@ -9352,7 +9352,7 @@
         <v>80.67</v>
       </c>
       <c r="M152" s="3">
-        <v>-2.91</v>
+        <v>-3.07</v>
       </c>
       <c r="N152" s="3">
         <v>-2.97</v>
@@ -9367,7 +9367,7 @@
         <v>4.09</v>
       </c>
       <c r="R152" s="3">
-        <v>-2.97</v>
+        <v>5.47</v>
       </c>
       <c r="S152" t="str">
         <v/>
@@ -9399,7 +9399,7 @@
         <v>48.67</v>
       </c>
       <c r="I153" s="1">
-        <v>8510128</v>
+        <v>8639491</v>
       </c>
       <c r="J153" s="1">
         <v>354.97</v>
@@ -9411,7 +9411,7 @@
         <v>425.97</v>
       </c>
       <c r="M153" s="3">
-        <v>24.11</v>
+        <v>4.06</v>
       </c>
       <c r="N153" s="3">
         <v>4.25</v>
@@ -9426,7 +9426,7 @@
         <v>57.4</v>
       </c>
       <c r="R153" s="3">
-        <v>4.25</v>
+        <v>44.84</v>
       </c>
       <c r="S153" t="str">
         <v/>
@@ -9458,7 +9458,7 @@
         <v>4.29</v>
       </c>
       <c r="I154" s="1">
-        <v>1269968</v>
+        <v>1354690</v>
       </c>
       <c r="J154" s="1">
         <v>366</v>
@@ -9470,7 +9470,7 @@
         <v>394.59</v>
       </c>
       <c r="M154" s="3">
-        <v>7.01</v>
+        <v>-4.92</v>
       </c>
       <c r="N154" s="3">
         <v>-5.28</v>
@@ -9485,7 +9485,7 @@
         <v>47.96</v>
       </c>
       <c r="R154" s="3">
-        <v>-5.28</v>
+        <v>45.45</v>
       </c>
       <c r="S154" t="str">
         <v/>
@@ -9517,7 +9517,7 @@
         <v>-16.12</v>
       </c>
       <c r="I155" s="1">
-        <v>523187</v>
+        <v>527783</v>
       </c>
       <c r="J155" s="1">
         <v>2019.54</v>
@@ -9529,7 +9529,7 @@
         <v>1854.37</v>
       </c>
       <c r="M155" s="3">
-        <v>-84.08</v>
+        <v>-25.75</v>
       </c>
       <c r="N155" s="3">
         <v>-26.56</v>
@@ -9544,7 +9544,7 @@
         <v>-155.08</v>
       </c>
       <c r="R155" s="3">
-        <v>-26.56</v>
+        <v>-102.39</v>
       </c>
       <c r="S155" t="str">
         <v/>
@@ -9576,7 +9576,7 @@
         <v>-16.66</v>
       </c>
       <c r="I156" s="1">
-        <v>930019</v>
+        <v>969243</v>
       </c>
       <c r="J156" s="1">
         <v>1869.94</v>
@@ -9588,7 +9588,7 @@
         <v>1885.75</v>
       </c>
       <c r="M156" s="3">
-        <v>-32.98</v>
+        <v>-45.71</v>
       </c>
       <c r="N156" s="3">
         <v>-49.66</v>
@@ -9603,7 +9603,7 @@
         <v>19.23</v>
       </c>
       <c r="R156" s="3">
-        <v>-49.66</v>
+        <v>53.93</v>
       </c>
       <c r="S156" t="str">
         <v/>
@@ -9635,7 +9635,7 @@
         <v>-24.84</v>
       </c>
       <c r="I157" s="1">
-        <v>1083985</v>
+        <v>1103124</v>
       </c>
       <c r="J157" s="1">
         <v>443.12</v>
@@ -9647,7 +9647,7 @@
         <v>388.31</v>
       </c>
       <c r="M157" s="3">
-        <v>-20.2</v>
+        <v>-1.85</v>
       </c>
       <c r="N157" s="3">
         <v>-2.48</v>
@@ -9662,7 +9662,7 @@
         <v>-38.31</v>
       </c>
       <c r="R157" s="3">
-        <v>-2.48</v>
+        <v>-28.09</v>
       </c>
       <c r="S157" t="str">
         <v/>
@@ -9694,7 +9694,7 @@
         <v>20.64</v>
       </c>
       <c r="I158" s="1">
-        <v>351937</v>
+        <v>352954</v>
       </c>
       <c r="J158" s="1">
         <v>1002.89</v>
@@ -9706,7 +9706,7 @@
         <v>1149.65</v>
       </c>
       <c r="M158" s="3">
-        <v>45.81</v>
+        <v>11.62</v>
       </c>
       <c r="N158" s="3">
         <v>6.95</v>
@@ -9721,7 +9721,7 @@
         <v>82.19</v>
       </c>
       <c r="R158" s="3">
-        <v>6.95</v>
+        <v>65.5</v>
       </c>
       <c r="S158" t="str">
         <v/>
@@ -9753,7 +9753,7 @@
         <v>-15.26</v>
       </c>
       <c r="I159" s="1">
-        <v>3498458</v>
+        <v>3558062</v>
       </c>
       <c r="J159" s="1">
         <v>344.84</v>
@@ -9765,7 +9765,7 @@
         <v>316.67</v>
       </c>
       <c r="M159" s="3">
-        <v>-14.34</v>
+        <v>-3.1</v>
       </c>
       <c r="N159" s="3">
         <v>-5.09</v>
@@ -9780,7 +9780,7 @@
         <v>-16.86</v>
       </c>
       <c r="R159" s="3">
-        <v>-5.09</v>
+        <v>-6.49</v>
       </c>
       <c r="S159" t="str">
         <v/>
@@ -9812,7 +9812,7 @@
         <v>-15.91</v>
       </c>
       <c r="I160" s="1">
-        <v>503460</v>
+        <v>510963</v>
       </c>
       <c r="J160" s="1">
         <v>1752.43</v>
@@ -9824,7 +9824,7 @@
         <v>1576.76</v>
       </c>
       <c r="M160" s="3">
-        <v>-48.99</v>
+        <v>37.56</v>
       </c>
       <c r="N160" s="3">
         <v>27.52</v>
@@ -9839,7 +9839,7 @@
         <v>-22.98</v>
       </c>
       <c r="R160" s="3">
-        <v>27.52</v>
+        <v>23.16</v>
       </c>
       <c r="S160" t="str">
         <v/>
@@ -9871,7 +9871,7 @@
         <v>-24.29</v>
       </c>
       <c r="I161" s="1">
-        <v>286608</v>
+        <v>294423</v>
       </c>
       <c r="J161" s="1">
         <v>1470.81</v>
@@ -9883,7 +9883,7 @@
         <v>1405.93</v>
       </c>
       <c r="M161" s="3">
-        <v>-68.3</v>
+        <v>-49.01</v>
       </c>
       <c r="N161" s="3">
         <v>-49.7</v>
@@ -9898,7 +9898,7 @@
         <v>14.68</v>
       </c>
       <c r="R161" s="3">
-        <v>-49.7</v>
+        <v>88.84</v>
       </c>
       <c r="S161" t="str">
         <v/>
@@ -9930,7 +9930,7 @@
         <v>-2.29</v>
       </c>
       <c r="I162" s="1">
-        <v>1486132</v>
+        <v>1493862</v>
       </c>
       <c r="J162" s="1">
         <v>1006</v>
@@ -9942,7 +9942,7 @@
         <v>1046.87</v>
       </c>
       <c r="M162" s="3">
-        <v>2.78</v>
+        <v>-17.01</v>
       </c>
       <c r="N162" s="3">
         <v>-16.86</v>
@@ -9957,7 +9957,7 @@
         <v>93.74</v>
       </c>
       <c r="R162" s="3">
-        <v>-16.86</v>
+        <v>88.11</v>
       </c>
       <c r="S162" t="str">
         <v/>
@@ -9989,7 +9989,7 @@
         <v>-7.21</v>
       </c>
       <c r="I163" s="1">
-        <v>302407</v>
+        <v>304532</v>
       </c>
       <c r="J163" s="1">
         <v>736.22</v>
@@ -10001,7 +10001,7 @@
         <v>725.49</v>
       </c>
       <c r="M163" s="3">
-        <v>-17.43</v>
+        <v>-8.91</v>
       </c>
       <c r="N163" s="3">
         <v>-12.72</v>
@@ -10016,7 +10016,7 @@
         <v>8.01</v>
       </c>
       <c r="R163" s="3">
-        <v>-12.72</v>
+        <v>20.36</v>
       </c>
       <c r="S163" t="str">
         <v/>
@@ -10048,7 +10048,7 @@
         <v>-3.52</v>
       </c>
       <c r="I164" s="1">
-        <v>1142228</v>
+        <v>1187523</v>
       </c>
       <c r="J164" s="1">
         <v>1365.08</v>
@@ -10060,7 +10060,7 @@
         <v>1399</v>
       </c>
       <c r="M164" s="3">
-        <v>-17.52</v>
+        <v>-31.02</v>
       </c>
       <c r="N164" s="3">
         <v>-26.81</v>
@@ -10075,7 +10075,7 @@
         <v>57.18</v>
       </c>
       <c r="R164" s="3">
-        <v>-26.81</v>
+        <v>59.04</v>
       </c>
       <c r="S164" t="str">
         <v/>
@@ -10107,7 +10107,7 @@
         <v>-5.2</v>
       </c>
       <c r="I165" s="1">
-        <v>825777</v>
+        <v>832228</v>
       </c>
       <c r="J165" s="1">
         <v>533.35</v>
@@ -10119,7 +10119,7 @@
         <v>532.68</v>
       </c>
       <c r="M165" s="3">
-        <v>-2.64</v>
+        <v>-3.53</v>
       </c>
       <c r="N165" s="3">
         <v>-0.86</v>
@@ -10134,7 +10134,7 @@
         <v>-8.93</v>
       </c>
       <c r="R165" s="3">
-        <v>-0.86</v>
+        <v>-2.88</v>
       </c>
       <c r="S165" t="str">
         <v/>
@@ -10166,7 +10166,7 @@
         <v>-0.95</v>
       </c>
       <c r="I166" s="1">
-        <v>1206094</v>
+        <v>1220263</v>
       </c>
       <c r="J166" s="1">
         <v>444.28</v>
@@ -10178,7 +10178,7 @@
         <v>436.78</v>
       </c>
       <c r="M166" s="3">
-        <v>-12.24</v>
+        <v>-9.28</v>
       </c>
       <c r="N166" s="3">
         <v>-10.67</v>
@@ -10193,7 +10193,7 @@
         <v>10.45</v>
       </c>
       <c r="R166" s="3">
-        <v>-10.67</v>
+        <v>11.24</v>
       </c>
       <c r="S166" t="str">
         <v/>
@@ -10225,7 +10225,7 @@
         <v>-15.43</v>
       </c>
       <c r="I167" s="1">
-        <v>167160</v>
+        <v>168761</v>
       </c>
       <c r="J167" s="1">
         <v>1157.41</v>
@@ -10237,7 +10237,7 @@
         <v>1207.61</v>
       </c>
       <c r="M167" s="3">
-        <v>-3.92</v>
+        <v>-31.7</v>
       </c>
       <c r="N167" s="3">
         <v>-30.4</v>
@@ -10252,7 +10252,7 @@
         <v>70.01</v>
       </c>
       <c r="R167" s="3">
-        <v>-30.4</v>
+        <v>91.95</v>
       </c>
       <c r="S167" t="str">
         <v/>
@@ -10284,7 +10284,7 @@
         <v>-11.34</v>
       </c>
       <c r="I168" s="1">
-        <v>1694743</v>
+        <v>1696837</v>
       </c>
       <c r="J168" s="1">
         <v>1101.94</v>
@@ -10296,7 +10296,7 @@
         <v>1115.16</v>
       </c>
       <c r="M168" s="3">
-        <v>-9.68</v>
+        <v>-11.11</v>
       </c>
       <c r="N168" s="3">
         <v>-15.93</v>
@@ -10311,7 +10311,7 @@
         <v>59.46</v>
       </c>
       <c r="R168" s="3">
-        <v>-15.93</v>
+        <v>81.23</v>
       </c>
       <c r="S168" t="str">
         <v/>
@@ -10343,7 +10343,7 @@
         <v>-20.58</v>
       </c>
       <c r="I169" s="1">
-        <v>1992215</v>
+        <v>2042848</v>
       </c>
       <c r="J169" s="1">
         <v>1022.29</v>
@@ -10355,7 +10355,7 @@
         <v>984.18</v>
       </c>
       <c r="M169" s="3">
-        <v>-43.32</v>
+        <v>-47.63</v>
       </c>
       <c r="N169" s="3">
         <v>-39.28</v>
@@ -10370,7 +10370,7 @@
         <v>18.93</v>
       </c>
       <c r="R169" s="3">
-        <v>-39.28</v>
+        <v>59.1</v>
       </c>
       <c r="S169" t="str">
         <v/>
@@ -10402,7 +10402,7 @@
         <v>-17.6</v>
       </c>
       <c r="I170" s="1">
-        <v>287618</v>
+        <v>290592</v>
       </c>
       <c r="J170" s="1">
         <v>2410.79</v>
@@ -10414,7 +10414,7 @@
         <v>2334.02</v>
       </c>
       <c r="M170" s="3">
-        <v>-107.39</v>
+        <v>-69.44</v>
       </c>
       <c r="N170" s="3">
         <v>-81.9</v>
@@ -10429,7 +10429,7 @@
         <v>94.21</v>
       </c>
       <c r="R170" s="3">
-        <v>-81.9</v>
+        <v>213.84</v>
       </c>
       <c r="S170" t="str">
         <v/>
@@ -10461,7 +10461,7 @@
         <v>1.18</v>
       </c>
       <c r="I171" s="1">
-        <v>2753410</v>
+        <v>2826003</v>
       </c>
       <c r="J171" s="1">
         <v>373.04</v>
@@ -10473,7 +10473,7 @@
         <v>362.16</v>
       </c>
       <c r="M171" s="3">
-        <v>-8.52</v>
+        <v>-12.35</v>
       </c>
       <c r="N171" s="3">
         <v>-12.2</v>
@@ -10488,7 +10488,7 @@
         <v>49.42</v>
       </c>
       <c r="R171" s="3">
-        <v>-12.2</v>
+        <v>52.1</v>
       </c>
       <c r="S171" t="str">
         <v/>
@@ -10520,7 +10520,7 @@
         <v>-0.02</v>
       </c>
       <c r="I172" s="1">
-        <v>308998</v>
+        <v>310831</v>
       </c>
       <c r="J172" s="1">
         <v>12092.03</v>
@@ -10532,7 +10532,7 @@
         <v>13662.76</v>
       </c>
       <c r="M172" s="3">
-        <v>87.5</v>
+        <v>-339.59</v>
       </c>
       <c r="N172" s="3">
         <v>-298.91</v>
@@ -10547,7 +10547,7 @@
         <v>421.08</v>
       </c>
       <c r="R172" s="3">
-        <v>-298.91</v>
+        <v>708.12</v>
       </c>
       <c r="S172" t="str">
         <v/>
@@ -10579,7 +10579,7 @@
         <v>-6.24</v>
       </c>
       <c r="I173" s="1">
-        <v>7692708</v>
+        <v>7888611</v>
       </c>
       <c r="J173" s="1">
         <v>357.06</v>
@@ -10591,7 +10591,7 @@
         <v>328.06</v>
       </c>
       <c r="M173" s="3">
-        <v>-13.15</v>
+        <v>-5.14</v>
       </c>
       <c r="N173" s="3">
         <v>-5.03</v>
@@ -10606,7 +10606,7 @@
         <v>5.94</v>
       </c>
       <c r="R173" s="3">
-        <v>-5.03</v>
+        <v>14.9</v>
       </c>
       <c r="S173" t="str">
         <v/>
@@ -10638,7 +10638,7 @@
         <v>-15.27</v>
       </c>
       <c r="I174" s="1">
-        <v>865785</v>
+        <v>878281</v>
       </c>
       <c r="J174" s="1">
         <v>2852.81</v>
@@ -10650,7 +10650,7 @@
         <v>2550.48</v>
       </c>
       <c r="M174" s="3">
-        <v>-141.66</v>
+        <v>-16.75</v>
       </c>
       <c r="N174" s="3">
         <v>-43.58</v>
@@ -10665,7 +10665,7 @@
         <v>-47.94</v>
       </c>
       <c r="R174" s="3">
-        <v>-43.58</v>
+        <v>28.89</v>
       </c>
       <c r="S174" t="str">
         <v/>
@@ -10697,7 +10697,7 @@
         <v>10.62</v>
       </c>
       <c r="I175" s="1">
-        <v>270470</v>
+        <v>276028</v>
       </c>
       <c r="J175" s="1">
         <v>3096.99</v>
@@ -10709,7 +10709,7 @@
         <v>3263.51</v>
       </c>
       <c r="M175" s="3">
-        <v>-45.76</v>
+        <v>-77.63</v>
       </c>
       <c r="N175" s="3">
         <v>-38.8</v>
@@ -10724,7 +10724,7 @@
         <v>44.96</v>
       </c>
       <c r="R175" s="3">
-        <v>-38.8</v>
+        <v>51.76</v>
       </c>
       <c r="S175" t="str">
         <v/>
@@ -10756,7 +10756,7 @@
         <v>22.32</v>
       </c>
       <c r="I176" s="1">
-        <v>409882</v>
+        <v>429055</v>
       </c>
       <c r="J176" s="1">
         <v>1872.46</v>
@@ -10768,7 +10768,7 @@
         <v>1973.13</v>
       </c>
       <c r="M176" s="3">
-        <v>2</v>
+        <v>-46.64</v>
       </c>
       <c r="N176" s="3">
         <v>-45.67</v>
@@ -10783,7 +10783,7 @@
         <v>215.12</v>
       </c>
       <c r="R176" s="3">
-        <v>-45.67</v>
+        <v>189.04</v>
       </c>
       <c r="S176" t="str">
         <v/>
@@ -10815,7 +10815,7 @@
         <v>-12.09</v>
       </c>
       <c r="I177" s="1">
-        <v>494609</v>
+        <v>503541</v>
       </c>
       <c r="J177" s="1">
         <v>2573.06</v>
@@ -10827,7 +10827,7 @@
         <v>2445.22</v>
       </c>
       <c r="M177" s="3">
-        <v>-76.56</v>
+        <v>-26.49</v>
       </c>
       <c r="N177" s="3">
         <v>-42.17</v>
@@ -10842,7 +10842,7 @@
         <v>133.25</v>
       </c>
       <c r="R177" s="3">
-        <v>-42.17</v>
+        <v>201.68</v>
       </c>
       <c r="S177" t="str">
         <v/>
@@ -10874,7 +10874,7 @@
         <v>2.23</v>
       </c>
       <c r="I178" s="1">
-        <v>66855</v>
+        <v>67193</v>
       </c>
       <c r="J178" s="1">
         <v>7230.39</v>
@@ -10886,7 +10886,7 @@
         <v>7080.37</v>
       </c>
       <c r="M178" s="3">
-        <v>-217.09</v>
+        <v>-152.12</v>
       </c>
       <c r="N178" s="3">
         <v>-161.8</v>
@@ -10901,7 +10901,7 @@
         <v>521.18</v>
       </c>
       <c r="R178" s="3">
-        <v>-161.8</v>
+        <v>725.32</v>
       </c>
       <c r="S178" t="str">
         <v/>
@@ -10933,7 +10933,7 @@
         <v>-23.85</v>
       </c>
       <c r="I179" s="1">
-        <v>4496371</v>
+        <v>4513745</v>
       </c>
       <c r="J179" s="1">
         <v>123.04</v>
@@ -10945,7 +10945,7 @@
         <v>112.61</v>
       </c>
       <c r="M179" s="3">
-        <v>-5.57</v>
+        <v>-1.65</v>
       </c>
       <c r="N179" s="3">
         <v>-1.8</v>
@@ -10960,7 +10960,7 @@
         <v>-9.74</v>
       </c>
       <c r="R179" s="3">
-        <v>-1.8</v>
+        <v>-4.67</v>
       </c>
       <c r="S179" t="str">
         <v/>
@@ -10992,7 +10992,7 @@
         <v>-19.98</v>
       </c>
       <c r="I180" s="1">
-        <v>1154925</v>
+        <v>1226363</v>
       </c>
       <c r="J180" s="1">
         <v>2163.31</v>
@@ -11004,7 +11004,7 @@
         <v>1956.95</v>
       </c>
       <c r="M180" s="3">
-        <v>-96.95</v>
+        <v>-25.24</v>
       </c>
       <c r="N180" s="3">
         <v>-31.24</v>
@@ -11019,7 +11019,7 @@
         <v>-136.14</v>
       </c>
       <c r="R180" s="3">
-        <v>-31.24</v>
+        <v>-85.49</v>
       </c>
       <c r="S180" t="str">
         <v/>
@@ -11051,7 +11051,7 @@
         <v>12.33</v>
       </c>
       <c r="I181" s="1">
-        <v>4958081</v>
+        <v>4983682</v>
       </c>
       <c r="J181" s="1">
         <v>176.7</v>
@@ -11063,7 +11063,7 @@
         <v>171.82</v>
       </c>
       <c r="M181" s="3">
-        <v>-3.72</v>
+        <v>-2.68</v>
       </c>
       <c r="N181" s="3">
         <v>-2.28</v>
@@ -11078,7 +11078,7 @@
         <v>-5.47</v>
       </c>
       <c r="R181" s="3">
-        <v>-2.28</v>
+        <v>-8.56</v>
       </c>
       <c r="S181" t="str">
         <v/>
@@ -11110,7 +11110,7 @@
         <v>-10.84</v>
       </c>
       <c r="I182" s="1">
-        <v>11279676</v>
+        <v>11815153</v>
       </c>
       <c r="J182" s="1">
         <v>77.45</v>
@@ -11122,7 +11122,7 @@
         <v>83.73</v>
       </c>
       <c r="M182" s="3">
-        <v>1.18</v>
+        <v>-1.82</v>
       </c>
       <c r="N182" s="3">
         <v>-1.48</v>
@@ -11137,7 +11137,7 @@
         <v>2.77</v>
       </c>
       <c r="R182" s="3">
-        <v>-1.48</v>
+        <v>2.21</v>
       </c>
       <c r="S182" t="str">
         <v/>
@@ -11169,7 +11169,7 @@
         <v>-40.71</v>
       </c>
       <c r="I183" s="1">
-        <v>4727127</v>
+        <v>4800001</v>
       </c>
       <c r="J183" s="1">
         <v>283.2</v>
@@ -11181,7 +11181,7 @@
         <v>265.84</v>
       </c>
       <c r="M183" s="3">
-        <v>-14.19</v>
+        <v>-11.26</v>
       </c>
       <c r="N183" s="3">
         <v>-10.36</v>
@@ -11196,7 +11196,7 @@
         <v>-49.48</v>
       </c>
       <c r="R183" s="3">
-        <v>-10.36</v>
+        <v>-42.88</v>
       </c>
       <c r="S183" t="str">
         <v/>
@@ -11228,7 +11228,7 @@
         <v>-37.06</v>
       </c>
       <c r="I184" s="1">
-        <v>8311028</v>
+        <v>8414248</v>
       </c>
       <c r="J184" s="1">
         <v>97.19</v>
@@ -11240,7 +11240,7 @@
         <v>81.95</v>
       </c>
       <c r="M184" s="3">
-        <v>-6.37</v>
+        <v>-0.89</v>
       </c>
       <c r="N184" s="3">
         <v>-1.39</v>
@@ -11255,7 +11255,7 @@
         <v>-9.31</v>
       </c>
       <c r="R184" s="3">
-        <v>-1.39</v>
+        <v>-3.6</v>
       </c>
       <c r="S184" t="str">
         <v/>
@@ -11287,7 +11287,7 @@
         <v>1.36</v>
       </c>
       <c r="I185" s="1">
-        <v>794846</v>
+        <v>813750</v>
       </c>
       <c r="J185" s="1">
         <v>2781.95</v>
@@ -11299,7 +11299,7 @@
         <v>2853.93</v>
       </c>
       <c r="M185" s="3">
-        <v>-3.42</v>
+        <v>36.13</v>
       </c>
       <c r="N185" s="3">
         <v>11.74</v>
@@ -11314,7 +11314,7 @@
         <v>-37.43</v>
       </c>
       <c r="R185" s="3">
-        <v>11.74</v>
+        <v>29.08</v>
       </c>
       <c r="S185" t="str">
         <v/>
@@ -11346,7 +11346,7 @@
         <v>-28.17</v>
       </c>
       <c r="I186" s="1">
-        <v>32462186</v>
+        <v>33524133</v>
       </c>
       <c r="J186" s="1">
         <v>801.17</v>
@@ -11358,7 +11358,7 @@
         <v>718.07</v>
       </c>
       <c r="M186" s="3">
-        <v>-28.38</v>
+        <v>-1.49</v>
       </c>
       <c r="N186" s="3">
         <v>-2.85</v>
@@ -11373,7 +11373,7 @@
         <v>-37.56</v>
       </c>
       <c r="R186" s="3">
-        <v>-2.85</v>
+        <v>-9.43</v>
       </c>
       <c r="S186" t="str">
         <v/>
@@ -11405,7 +11405,7 @@
         <v>-14.15</v>
       </c>
       <c r="I187" s="1">
-        <v>4633404</v>
+        <v>4711070</v>
       </c>
       <c r="J187" s="1">
         <v>462.64</v>
@@ -11417,7 +11417,7 @@
         <v>426.77</v>
       </c>
       <c r="M187" s="3">
-        <v>-14.04</v>
+        <v>1.37</v>
       </c>
       <c r="N187" s="3">
         <v>2.45</v>
@@ -11432,7 +11432,7 @@
         <v>-8.62</v>
       </c>
       <c r="R187" s="3">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="S187" t="str">
         <v/>
@@ -11464,7 +11464,7 @@
         <v>-9.62</v>
       </c>
       <c r="I188" s="1">
-        <v>593671</v>
+        <v>609128</v>
       </c>
       <c r="J188" s="1">
         <v>11658.84</v>
@@ -11476,7 +11476,7 @@
         <v>11179.48</v>
       </c>
       <c r="M188" s="3">
-        <v>-244.9</v>
+        <v>-119.6</v>
       </c>
       <c r="N188" s="3">
         <v>-146.18</v>
@@ -11491,7 +11491,7 @@
         <v>198.6</v>
       </c>
       <c r="R188" s="3">
-        <v>-146.18</v>
+        <v>446.94</v>
       </c>
       <c r="S188" t="str">
         <v/>
@@ -11523,7 +11523,7 @@
         <v>5.33</v>
       </c>
       <c r="I189" s="1">
-        <v>289711</v>
+        <v>294308</v>
       </c>
       <c r="J189" s="1">
         <v>8426.55</v>
@@ -11535,7 +11535,7 @@
         <v>8598.42</v>
       </c>
       <c r="M189" s="3">
-        <v>-86.63</v>
+        <v>-97.36</v>
       </c>
       <c r="N189" s="3">
         <v>-116.75</v>
@@ -11550,7 +11550,7 @@
         <v>825.05</v>
       </c>
       <c r="R189" s="3">
-        <v>-116.75</v>
+        <v>861.16</v>
       </c>
       <c r="S189" t="str">
         <v/>
@@ -11582,7 +11582,7 @@
         <v>-34.57</v>
       </c>
       <c r="I190" s="1">
-        <v>106929</v>
+        <v>107848</v>
       </c>
       <c r="J190" s="1">
         <v>2126.16</v>
@@ -11594,7 +11594,7 @@
         <v>2003.26</v>
       </c>
       <c r="M190" s="3">
-        <v>-118.93</v>
+        <v>-50.48</v>
       </c>
       <c r="N190" s="3">
         <v>-53.73</v>
@@ -11609,7 +11609,7 @@
         <v>47.71</v>
       </c>
       <c r="R190" s="3">
-        <v>-53.73</v>
+        <v>195.27</v>
       </c>
       <c r="S190" t="str">
         <v/>
@@ -11641,7 +11641,7 @@
         <v>-25.81</v>
       </c>
       <c r="I191" s="1">
-        <v>364320</v>
+        <v>366812</v>
       </c>
       <c r="J191" s="1">
         <v>1301.47</v>
@@ -11653,7 +11653,7 @@
         <v>1216.92</v>
       </c>
       <c r="M191" s="3">
-        <v>-64.38</v>
+        <v>-28.53</v>
       </c>
       <c r="N191" s="3">
         <v>-35.99</v>
@@ -11668,7 +11668,7 @@
         <v>10.97</v>
       </c>
       <c r="R191" s="3">
-        <v>-35.99</v>
+        <v>76.23</v>
       </c>
       <c r="S191" t="str">
         <v/>
@@ -11700,7 +11700,7 @@
         <v>-39.48</v>
       </c>
       <c r="I192" s="1">
-        <v>3332034</v>
+        <v>3369427</v>
       </c>
       <c r="J192" s="1">
         <v>94.04</v>
@@ -11712,7 +11712,7 @@
         <v>83.64</v>
       </c>
       <c r="M192" s="3">
-        <v>-6.15</v>
+        <v>-2.66</v>
       </c>
       <c r="N192" s="3">
         <v>-2.74</v>
@@ -11727,7 +11727,7 @@
         <v>-0.18</v>
       </c>
       <c r="R192" s="3">
-        <v>-2.74</v>
+        <v>4.78</v>
       </c>
       <c r="S192" t="str">
         <v/>
@@ -11759,7 +11759,7 @@
         <v>9.34</v>
       </c>
       <c r="I193" s="1">
-        <v>415454</v>
+        <v>422465</v>
       </c>
       <c r="J193" s="1">
         <v>8064.01</v>
@@ -11771,7 +11771,7 @@
         <v>8571.03</v>
       </c>
       <c r="M193" s="3">
-        <v>11.12</v>
+        <v>-260.78</v>
       </c>
       <c r="N193" s="3">
         <v>-231.33</v>
@@ -11786,7 +11786,7 @@
         <v>548.45</v>
       </c>
       <c r="R193" s="3">
-        <v>-231.33</v>
+        <v>565.66</v>
       </c>
       <c r="S193" t="str">
         <v/>
@@ -11818,7 +11818,7 @@
         <v>26.97</v>
       </c>
       <c r="I194" s="1">
-        <v>3841197</v>
+        <v>3892230</v>
       </c>
       <c r="J194" s="1">
         <v>288.9</v>
@@ -11830,7 +11830,7 @@
         <v>334.15</v>
       </c>
       <c r="M194" s="3">
-        <v>16.91</v>
+        <v>1.77</v>
       </c>
       <c r="N194" s="3">
         <v>1.25</v>
@@ -11845,7 +11845,7 @@
         <v>33.25</v>
       </c>
       <c r="R194" s="3">
-        <v>1.25</v>
+        <v>23.05</v>
       </c>
       <c r="S194" t="str">
         <v/>
@@ -11877,7 +11877,7 @@
         <v>14.13</v>
       </c>
       <c r="I195" s="1">
-        <v>321056968</v>
+        <v>323539893</v>
       </c>
       <c r="J195" s="1">
         <v>12.3</v>
@@ -11889,7 +11889,7 @@
         <v>13.87</v>
       </c>
       <c r="M195" s="3">
-        <v>0.28</v>
+        <v>-0.45</v>
       </c>
       <c r="N195" s="3">
         <v>-0.38</v>
@@ -11904,7 +11904,7 @@
         <v>0.87</v>
       </c>
       <c r="R195" s="3">
-        <v>-0.38</v>
+        <v>0.43</v>
       </c>
       <c r="S195" t="str">
         <v/>
@@ -11936,7 +11936,7 @@
         <v>-45.56</v>
       </c>
       <c r="I196" s="1">
-        <v>1951177</v>
+        <v>1970644</v>
       </c>
       <c r="J196" s="1">
         <v>262.11</v>
@@ -11948,7 +11948,7 @@
         <v>209.75</v>
       </c>
       <c r="M196" s="3">
-        <v>-21.23</v>
+        <v>-4.01</v>
       </c>
       <c r="N196" s="3">
         <v>-4.66</v>
@@ -11963,7 +11963,7 @@
         <v>-28.19</v>
       </c>
       <c r="R196" s="3">
-        <v>-4.66</v>
+        <v>-7.81</v>
       </c>
       <c r="S196" t="str">
         <v/>
@@ -11995,7 +11995,7 @@
         <v>-11.7</v>
       </c>
       <c r="I197" s="1">
-        <v>876796</v>
+        <v>878350</v>
       </c>
       <c r="J197" s="1">
         <v>550.67</v>
@@ -12007,7 +12007,7 @@
         <v>552.43</v>
       </c>
       <c r="M197" s="3">
-        <v>-11.55</v>
+        <v>-7.71</v>
       </c>
       <c r="N197" s="3">
         <v>-11.11</v>
@@ -12022,7 +12022,7 @@
         <v>9.7</v>
       </c>
       <c r="R197" s="3">
-        <v>-11.11</v>
+        <v>34.24</v>
       </c>
       <c r="S197" t="str">
         <v/>
@@ -12054,7 +12054,7 @@
         <v>-2.98</v>
       </c>
       <c r="I198" s="1">
-        <v>7991259</v>
+        <v>8308852</v>
       </c>
       <c r="J198" s="1">
         <v>974.58</v>
@@ -12066,7 +12066,7 @@
         <v>1030.47</v>
       </c>
       <c r="M198" s="3">
-        <v>2.9</v>
+        <v>-18.24</v>
       </c>
       <c r="N198" s="3">
         <v>-21.14</v>
@@ -12081,7 +12081,7 @@
         <v>59.23</v>
       </c>
       <c r="R198" s="3">
-        <v>-21.14</v>
+        <v>64.6</v>
       </c>
       <c r="S198" t="str">
         <v/>
@@ -12113,7 +12113,7 @@
         <v>18.05</v>
       </c>
       <c r="I199" s="1">
-        <v>384306</v>
+        <v>387722</v>
       </c>
       <c r="J199" s="1">
         <v>1040.64</v>
@@ -12125,7 +12125,7 @@
         <v>1144.54</v>
       </c>
       <c r="M199" s="3">
-        <v>12.93</v>
+        <v>-26.63</v>
       </c>
       <c r="N199" s="3">
         <v>-28.13</v>
@@ -12140,7 +12140,7 @@
         <v>137.29</v>
       </c>
       <c r="R199" s="3">
-        <v>-28.13</v>
+        <v>131.39</v>
       </c>
       <c r="S199" t="str">
         <v/>
@@ -12172,7 +12172,7 @@
         <v>-21.92</v>
       </c>
       <c r="I200" s="1">
-        <v>1883838</v>
+        <v>1901670</v>
       </c>
       <c r="J200" s="1">
         <v>123.69</v>
@@ -12184,7 +12184,7 @@
         <v>115.54</v>
       </c>
       <c r="M200" s="3">
-        <v>-5.81</v>
+        <v>-2.71</v>
       </c>
       <c r="N200" s="3">
         <v>-3.21</v>
@@ -12199,7 +12199,7 @@
         <v>-13.03</v>
       </c>
       <c r="R200" s="3">
-        <v>-3.21</v>
+        <v>-10.03</v>
       </c>
       <c r="S200" t="str">
         <v/>
@@ -12231,7 +12231,7 @@
         <v>-30.01</v>
       </c>
       <c r="I201" s="1">
-        <v>12878711</v>
+        <v>13258477</v>
       </c>
       <c r="J201" s="1">
         <v>1234.08</v>
@@ -12243,7 +12243,7 @@
         <v>1086.58</v>
       </c>
       <c r="M201" s="3">
-        <v>-44.73</v>
+        <v>11</v>
       </c>
       <c r="N201" s="3">
         <v>-7.73</v>
@@ -12258,7 +12258,7 @@
         <v>-136.62</v>
       </c>
       <c r="R201" s="3">
-        <v>-7.73</v>
+        <v>-97.22</v>
       </c>
       <c r="S201" t="str">
         <v/>
@@ -12290,7 +12290,7 @@
         <v>-13.68</v>
       </c>
       <c r="I202" s="1">
-        <v>3209080</v>
+        <v>3222416</v>
       </c>
       <c r="J202" s="1">
         <v>392.8</v>
@@ -12302,7 +12302,7 @@
         <v>390.24</v>
       </c>
       <c r="M202" s="3">
-        <v>-11.33</v>
+        <v>-13.27</v>
       </c>
       <c r="N202" s="3">
         <v>-12.3</v>
@@ -12317,7 +12317,7 @@
         <v>15.4</v>
       </c>
       <c r="R202" s="3">
-        <v>-12.3</v>
+        <v>19.8</v>
       </c>
       <c r="S202" t="str">
         <v/>
@@ -12349,7 +12349,7 @@
         <v>-2.95</v>
       </c>
       <c r="I203" s="1">
-        <v>798372</v>
+        <v>805992</v>
       </c>
       <c r="J203" s="1">
         <v>1022.13</v>
@@ -12361,7 +12361,7 @@
         <v>1164.74</v>
       </c>
       <c r="M203" s="3">
-        <v>19.68</v>
+        <v>-30.95</v>
       </c>
       <c r="N203" s="3">
         <v>-26.34</v>
@@ -12376,7 +12376,7 @@
         <v>-0.28</v>
       </c>
       <c r="R203" s="3">
-        <v>-26.34</v>
+        <v>5.68</v>
       </c>
       <c r="S203" t="str">
         <v/>
@@ -12408,7 +12408,7 @@
         <v>37.06</v>
       </c>
       <c r="I204" s="1">
-        <v>726599</v>
+        <v>736433</v>
       </c>
       <c r="J204" s="1">
         <v>1440.77</v>
@@ -12420,7 +12420,7 @@
         <v>1667.08</v>
       </c>
       <c r="M204" s="3">
-        <v>75.04</v>
+        <v>-2.5</v>
       </c>
       <c r="N204" s="3">
         <v>5.02</v>
@@ -12435,7 +12435,7 @@
         <v>146.84</v>
       </c>
       <c r="R204" s="3">
-        <v>5.02</v>
+        <v>109.42</v>
       </c>
       <c r="S204" t="str">
         <v/>
@@ -12467,7 +12467,7 @@
         <v>-29.66</v>
       </c>
       <c r="I205" s="1">
-        <v>847134</v>
+        <v>850775</v>
       </c>
       <c r="J205" s="1">
         <v>4546.19</v>
@@ -12479,7 +12479,7 @@
         <v>4359.22</v>
       </c>
       <c r="M205" s="3">
-        <v>-80.26</v>
+        <v>-15.15</v>
       </c>
       <c r="N205" s="3">
         <v>-64.65</v>
@@ -12494,7 +12494,7 @@
         <v>-292.86</v>
       </c>
       <c r="R205" s="3">
-        <v>-64.65</v>
+        <v>-193.12</v>
       </c>
       <c r="S205" t="str">
         <v/>
@@ -12526,7 +12526,7 @@
         <v>-15.44</v>
       </c>
       <c r="I206" s="1">
-        <v>7111535</v>
+        <v>7146693</v>
       </c>
       <c r="J206" s="1">
         <v>43.7</v>
@@ -12538,7 +12538,7 @@
         <v>44.35</v>
       </c>
       <c r="M206" s="3">
-        <v>0.42</v>
+        <v>0.04</v>
       </c>
       <c r="N206" s="3">
         <v>-0.1</v>
@@ -12553,7 +12553,7 @@
         <v>0.69</v>
       </c>
       <c r="R206" s="3">
-        <v>-0.1</v>
+        <v>1.07</v>
       </c>
       <c r="S206" t="str">
         <v/>
@@ -12585,7 +12585,7 @@
         <v>-24.32</v>
       </c>
       <c r="I207" s="1">
-        <v>5153162</v>
+        <v>5268186</v>
       </c>
       <c r="J207" s="1">
         <v>340.88</v>
@@ -12597,7 +12597,7 @@
         <v>305.68</v>
       </c>
       <c r="M207" s="3">
-        <v>-20.04</v>
+        <v>-6.52</v>
       </c>
       <c r="N207" s="3">
         <v>-7.64</v>
@@ -12612,7 +12612,7 @@
         <v>-33.96</v>
       </c>
       <c r="R207" s="3">
-        <v>-7.64</v>
+        <v>-23.3</v>
       </c>
       <c r="S207" t="str">
         <v/>
@@ -12644,7 +12644,7 @@
         <v>-54.2</v>
       </c>
       <c r="I208" s="1">
-        <v>1566219</v>
+        <v>1570789</v>
       </c>
       <c r="J208" s="1">
         <v>728.61</v>
@@ -12656,7 +12656,7 @@
         <v>555.66</v>
       </c>
       <c r="M208" s="3">
-        <v>-73.33</v>
+        <v>-7.5</v>
       </c>
       <c r="N208" s="3">
         <v>-16.33</v>
@@ -12671,7 +12671,7 @@
         <v>-185.66</v>
       </c>
       <c r="R208" s="3">
-        <v>-16.33</v>
+        <v>-127.87</v>
       </c>
       <c r="S208" t="str">
         <v/>
@@ -12703,7 +12703,7 @@
         <v>-43.31</v>
       </c>
       <c r="I209" s="1">
-        <v>1559262</v>
+        <v>1591356</v>
       </c>
       <c r="J209" s="1">
         <v>1581.66</v>
@@ -12715,7 +12715,7 @@
         <v>1539.92</v>
       </c>
       <c r="M209" s="3">
-        <v>-138.06</v>
+        <v>-156.59</v>
       </c>
       <c r="N209" s="3">
         <v>-170.67</v>
@@ -12730,7 +12730,7 @@
         <v>-12.21</v>
       </c>
       <c r="R209" s="3">
-        <v>-170.67</v>
+        <v>77</v>
       </c>
       <c r="S209" t="str">
         <v/>
@@ -12762,7 +12762,7 @@
         <v>-17.36</v>
       </c>
       <c r="I210" s="1">
-        <v>8036501</v>
+        <v>8047666</v>
       </c>
       <c r="J210" s="1">
         <v>251.32</v>
@@ -12774,7 +12774,7 @@
         <v>228.04</v>
       </c>
       <c r="M210" s="3">
-        <v>-14.97</v>
+        <v>-5.02</v>
       </c>
       <c r="N210" s="3">
         <v>-6.38</v>
@@ -12789,7 +12789,7 @@
         <v>-30.72</v>
       </c>
       <c r="R210" s="3">
-        <v>-6.38</v>
+        <v>-25.2</v>
       </c>
       <c r="S210" t="str">
         <v/>
@@ -12821,7 +12821,7 @@
         <v>19.31</v>
       </c>
       <c r="I211" s="1">
-        <v>946223</v>
+        <v>957323</v>
       </c>
       <c r="J211" s="1">
         <v>867.93</v>
@@ -12833,7 +12833,7 @@
         <v>1002.25</v>
       </c>
       <c r="M211" s="3">
-        <v>48.31</v>
+        <v>12.77</v>
       </c>
       <c r="N211" s="3">
         <v>13.51</v>
@@ -12848,7 +12848,7 @@
         <v>97.92</v>
       </c>
       <c r="R211" s="3">
-        <v>13.51</v>
+        <v>93.65</v>
       </c>
       <c r="S211" t="str">
         <v/>
@@ -12880,7 +12880,7 @@
         <v>-21.85</v>
       </c>
       <c r="I212" s="1">
-        <v>204901582</v>
+        <v>206773668</v>
       </c>
       <c r="J212" s="1">
         <v>21.74</v>
@@ -12892,7 +12892,7 @@
         <v>21.93</v>
       </c>
       <c r="M212" s="3">
-        <v>-0.75</v>
+        <v>-1.11</v>
       </c>
       <c r="N212" s="3">
         <v>-0.71</v>
@@ -12907,7 +12907,7 @@
         <v>-0.09</v>
       </c>
       <c r="R212" s="3">
-        <v>-0.71</v>
+        <v>0.05</v>
       </c>
       <c r="S212" t="str">
         <v/>
@@ -12939,7 +12939,7 @@
         <v>-8.52</v>
       </c>
       <c r="I213" s="1">
-        <v>725743</v>
+        <v>750602</v>
       </c>
       <c r="J213" s="1">
         <v>1141.01</v>
@@ -12951,7 +12951,7 @@
         <v>1284.36</v>
       </c>
       <c r="M213" s="3">
-        <v>35.56</v>
+        <v>-12.46</v>
       </c>
       <c r="N213" s="3">
         <v>-16.01</v>
@@ -12966,7 +12966,7 @@
         <v>-21.37</v>
       </c>
       <c r="R213" s="3">
-        <v>-16.01</v>
+        <v>-13.08</v>
       </c>
       <c r="S213" t="str">
         <v/>
@@ -12998,7 +12998,7 @@
         <v>-23.33</v>
       </c>
       <c r="I214" s="1">
-        <v>64289140</v>
+        <v>65237716</v>
       </c>
       <c r="J214" s="1">
         <v>48.42</v>
@@ -13010,7 +13010,7 @@
         <v>43.71</v>
       </c>
       <c r="M214" s="3">
-        <v>-3.14</v>
+        <v>-0.97</v>
       </c>
       <c r="N214" s="3">
         <v>-1.49</v>
@@ -13025,7 +13025,7 @@
         <v>-0.79</v>
       </c>
       <c r="R214" s="3">
-        <v>-1.49</v>
+        <v>1.7</v>
       </c>
       <c r="S214" t="str">
         <v/>
@@ -13057,7 +13057,7 @@
         <v>-47.47</v>
       </c>
       <c r="I215" s="1">
-        <v>8181523</v>
+        <v>8224708</v>
       </c>
       <c r="J215" s="1">
         <v>88.59</v>
@@ -13069,7 +13069,7 @@
         <v>72.54</v>
       </c>
       <c r="M215" s="3">
-        <v>-7.97</v>
+        <v>-1.96</v>
       </c>
       <c r="N215" s="3">
         <v>-1.85</v>
@@ -13084,7 +13084,7 @@
         <v>-17.04</v>
       </c>
       <c r="R215" s="3">
-        <v>-1.85</v>
+        <v>-8.46</v>
       </c>
       <c r="S215" t="str">
         <v/>
@@ -13116,7 +13116,7 @@
         <v>-2.63</v>
       </c>
       <c r="I216" s="1">
-        <v>12677595</v>
+        <v>12762071</v>
       </c>
       <c r="J216" s="1">
         <v>1285.53</v>
@@ -13128,7 +13128,7 @@
         <v>1244.29</v>
       </c>
       <c r="M216" s="3">
-        <v>-8.94</v>
+        <v>6.48</v>
       </c>
       <c r="N216" s="3">
         <v>2.6</v>
@@ -13143,7 +13143,7 @@
         <v>50.31</v>
       </c>
       <c r="R216" s="3">
-        <v>2.6</v>
+        <v>60.52</v>
       </c>
       <c r="S216" t="str">
         <v/>
